--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$23</f>
+              <f>'GPU Rental'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$23</f>
+              <f>'GPU Rental'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$23</f>
+              <f>'GPU Rental'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$23</f>
+              <f>'GPU Rental'!$E$2:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$23</f>
+              <f>'GPU Rental'!$F$2:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$23</f>
+              <f>'GPU Rental'!$G$2:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$23</f>
+              <f>'GPU Rental'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$23</f>
+              <f>'GPU Rental'!$H$2:$H$24</f>
             </numRef>
           </val>
         </ser>
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2831,8 +2831,58 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I24" s="4">
+        <f>IF(OR(B24="",B23=""),"",B24/B23-1)</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>IF(OR(C24="",C23=""),"",C24/C23-1)</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>IF(OR(D24="",D23=""),"",D24/D23-1)</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>IF(OR(E24="",E23=""),"",E24/E23-1)</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>IF(OR(F24="",F23=""),"",F24/F23-1)</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>IF(OR(G24="",G23=""),"",G24/G23-1)</f>
+        <v/>
+      </c>
+      <c r="O24" s="4">
+        <f>IF(OR(H24="",H23=""),"",H24/H23-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45824,7 +45874,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-13  (22 rows)</t>
+          <t>2026-08-23 to 2026-09-14  (23 rows)</t>
         </is>
       </c>
     </row>
@@ -45836,7 +45886,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-13 18:49 local</t>
+          <t>2026-09-14 15:54 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$21</f>
+              <f>'Daily Index'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$21</f>
+              <f>'Daily Index'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$21</f>
+              <f>'Daily Index'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$21</f>
+              <f>'Daily Index'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$21</f>
+              <f>'Daily Index'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$21</f>
+              <f>'Daily Index'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1562,8 +1562,86 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="E22" s="4">
+        <f>IF(OR(B22="",B21=""),"",B22/B21-1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>IF(OR(C22="",C21=""),"",C22/C21-1)</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(OR(D22="",D21=""),"",D22/D21-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1.7852</v>
+      </c>
+      <c r="E23" s="4">
+        <f>IF(OR(B23="",B22=""),"",B23/B22-1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>IF(OR(C23="",C22=""),"",C23/C22-1)</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(OR(D23="",D22=""),"",D23/D22-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>0.9681999999999999</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1.7063</v>
+      </c>
+      <c r="E24" s="4">
+        <f>IF(OR(B24="",B23=""),"",B24/B23-1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>IF(OR(C24="",C23=""),"",C24/C23-1)</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(OR(D24="",D23=""),"",D24/D23-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2835,7 +2913,9 @@
       <c r="A24" s="10" t="n">
         <v>46279</v>
       </c>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="5" t="n">
+        <v>2.66</v>
+      </c>
       <c r="C24" s="5" t="n">
         <v>1.58</v>
       </c>
@@ -2845,7 +2925,9 @@
       <c r="E24" s="5" t="n">
         <v>2.64</v>
       </c>
-      <c r="F24" s="5" t="n"/>
+      <c r="F24" s="5" t="n">
+        <v>5.72</v>
+      </c>
       <c r="G24" s="5" t="n">
         <v>7.2</v>
       </c>
@@ -2893,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN103"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15992,8 +16074,764 @@
         <v>2.2426</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>1.5804</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>1.7112</v>
+      </c>
+      <c r="G104" s="11" t="n">
+        <v>1.6303</v>
+      </c>
+      <c r="H104" s="11" t="n">
+        <v>1.5839</v>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="J104" s="11" t="n">
+        <v>1.4957</v>
+      </c>
+      <c r="K104" s="11" t="n">
+        <v>1.4174</v>
+      </c>
+      <c r="L104" s="11" t="n">
+        <v>1.3619</v>
+      </c>
+      <c r="M104" s="11" t="n">
+        <v>1.3291</v>
+      </c>
+      <c r="N104" s="11" t="n">
+        <v>1.3191</v>
+      </c>
+      <c r="O104" s="11" t="n">
+        <v>1.3319</v>
+      </c>
+      <c r="P104" s="11" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q104" s="11" t="n">
+        <v>1.3825</v>
+      </c>
+      <c r="R104" s="11" t="n">
+        <v>1.3938</v>
+      </c>
+      <c r="S104" s="11" t="n">
+        <v>1.4011</v>
+      </c>
+      <c r="T104" s="11" t="n">
+        <v>1.4044</v>
+      </c>
+      <c r="U104" s="11" t="n">
+        <v>1.4038</v>
+      </c>
+      <c r="V104" s="11" t="n">
+        <v>1.3992</v>
+      </c>
+      <c r="W104" s="11" t="n">
+        <v>1.3908</v>
+      </c>
+      <c r="X104" s="11" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="Y104" s="11" t="n">
+        <v>1.3619</v>
+      </c>
+      <c r="Z104" s="11" t="n">
+        <v>1.3416</v>
+      </c>
+      <c r="AA104" s="11" t="n">
+        <v>1.3174</v>
+      </c>
+      <c r="AB104" s="11" t="n">
+        <v>1.2891</v>
+      </c>
+      <c r="AC104" s="11" t="n">
+        <v>1.2621</v>
+      </c>
+      <c r="AD104" s="11" t="n">
+        <v>1.2387</v>
+      </c>
+      <c r="AE104" s="11" t="n">
+        <v>1.2189</v>
+      </c>
+      <c r="AF104" s="11" t="n">
+        <v>1.2027</v>
+      </c>
+      <c r="AG104" s="11" t="n">
+        <v>1.1901</v>
+      </c>
+      <c r="AH104" s="11" t="n">
+        <v>1.1811</v>
+      </c>
+      <c r="AI104" s="11" t="n">
+        <v>1.1757</v>
+      </c>
+      <c r="AJ104" s="11" t="n">
+        <v>1.1739</v>
+      </c>
+      <c r="AK104" s="11" t="n">
+        <v>1.1757</v>
+      </c>
+      <c r="AL104" s="11" t="n">
+        <v>1.1811</v>
+      </c>
+      <c r="AM104" s="11" t="n">
+        <v>1.1901</v>
+      </c>
+      <c r="AN104" s="11" t="n">
+        <v>1.2027</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1.5327</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>1.5981</v>
+      </c>
+      <c r="G105" s="11" t="n">
+        <v>1.6282</v>
+      </c>
+      <c r="H105" s="11" t="n">
+        <v>1.6229</v>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>1.6106</v>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="L105" s="11" t="n">
+        <v>1.5516</v>
+      </c>
+      <c r="M105" s="11" t="n">
+        <v>1.5284</v>
+      </c>
+      <c r="N105" s="11" t="n">
+        <v>1.5078</v>
+      </c>
+      <c r="O105" s="11" t="n">
+        <v>1.4911</v>
+      </c>
+      <c r="P105" s="11" t="n">
+        <v>1.4791</v>
+      </c>
+      <c r="Q105" s="11" t="n">
+        <v>1.4711</v>
+      </c>
+      <c r="R105" s="11" t="n">
+        <v>1.4652</v>
+      </c>
+      <c r="S105" s="11" t="n">
+        <v>1.4607</v>
+      </c>
+      <c r="T105" s="11" t="n">
+        <v>1.4571</v>
+      </c>
+      <c r="U105" s="11" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="V105" s="11" t="n">
+        <v>1.4511</v>
+      </c>
+      <c r="W105" s="11" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="X105" s="11" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="Y105" s="11" t="n">
+        <v>1.4415</v>
+      </c>
+      <c r="Z105" s="11" t="n">
+        <v>1.4374</v>
+      </c>
+      <c r="AA105" s="11" t="n">
+        <v>1.4327</v>
+      </c>
+      <c r="AB105" s="11" t="n">
+        <v>1.4274</v>
+      </c>
+      <c r="AC105" s="11" t="n">
+        <v>1.4213</v>
+      </c>
+      <c r="AD105" s="11" t="n">
+        <v>1.4147</v>
+      </c>
+      <c r="AE105" s="11" t="n">
+        <v>1.4078</v>
+      </c>
+      <c r="AF105" s="11" t="n">
+        <v>1.4008</v>
+      </c>
+      <c r="AG105" s="11" t="n">
+        <v>1.3937</v>
+      </c>
+      <c r="AH105" s="11" t="n">
+        <v>1.3867</v>
+      </c>
+      <c r="AI105" s="11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ105" s="11" t="n">
+        <v>1.3736</v>
+      </c>
+      <c r="AK105" s="11" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="AL105" s="11" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="AM105" s="11" t="n">
+        <v>1.3569</v>
+      </c>
+      <c r="AN105" s="11" t="n">
+        <v>1.3525</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>5.7206</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>5.6491</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G106" s="11" t="n">
+        <v>5.6049</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>5.3938</v>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>5.2899</v>
+      </c>
+      <c r="J106" s="11" t="n">
+        <v>5.2931</v>
+      </c>
+      <c r="K106" s="11" t="n">
+        <v>5.2478</v>
+      </c>
+      <c r="L106" s="11" t="n">
+        <v>5.1992</v>
+      </c>
+      <c r="M106" s="11" t="n">
+        <v>5.1472</v>
+      </c>
+      <c r="N106" s="11" t="n">
+        <v>5.0918</v>
+      </c>
+      <c r="O106" s="11" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P106" s="11" t="n">
+        <v>4.971</v>
+      </c>
+      <c r="Q106" s="11" t="n">
+        <v>4.7895</v>
+      </c>
+      <c r="R106" s="11" t="n">
+        <v>4.6436</v>
+      </c>
+      <c r="S106" s="11" t="n">
+        <v>4.5332</v>
+      </c>
+      <c r="T106" s="11" t="n">
+        <v>4.4584</v>
+      </c>
+      <c r="U106" s="11" t="n">
+        <v>4.4191</v>
+      </c>
+      <c r="V106" s="11" t="n">
+        <v>4.4154</v>
+      </c>
+      <c r="W106" s="11" t="n">
+        <v>4.4472</v>
+      </c>
+      <c r="X106" s="11" t="n">
+        <v>4.5145</v>
+      </c>
+      <c r="Y106" s="11" t="n">
+        <v>4.6174</v>
+      </c>
+      <c r="Z106" s="11" t="n">
+        <v>4.7559</v>
+      </c>
+      <c r="AA106" s="11" t="n">
+        <v>4.9299</v>
+      </c>
+      <c r="AB106" s="11" t="n">
+        <v>5.1394</v>
+      </c>
+      <c r="AC106" s="11" t="n">
+        <v>5.2991</v>
+      </c>
+      <c r="AD106" s="11" t="n">
+        <v>5.4374</v>
+      </c>
+      <c r="AE106" s="11" t="n">
+        <v>5.5544</v>
+      </c>
+      <c r="AF106" s="11" t="n">
+        <v>5.6502</v>
+      </c>
+      <c r="AG106" s="11" t="n">
+        <v>5.7247</v>
+      </c>
+      <c r="AH106" s="11" t="n">
+        <v>5.7779</v>
+      </c>
+      <c r="AI106" s="11" t="n">
+        <v>5.8098</v>
+      </c>
+      <c r="AJ106" s="11" t="n">
+        <v>5.8205</v>
+      </c>
+      <c r="AK106" s="11" t="n">
+        <v>5.8098</v>
+      </c>
+      <c r="AL106" s="11" t="n">
+        <v>5.7779</v>
+      </c>
+      <c r="AM106" s="11" t="n">
+        <v>5.7247</v>
+      </c>
+      <c r="AN106" s="11" t="n">
+        <v>5.6502</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>5.7206</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>5.5925</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>5.683</v>
+      </c>
+      <c r="G107" s="11" t="n">
+        <v>5.7057</v>
+      </c>
+      <c r="H107" s="11" t="n">
+        <v>5.6519</v>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>5.5881</v>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>5.5372</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>5.4991</v>
+      </c>
+      <c r="L107" s="11" t="n">
+        <v>5.4647</v>
+      </c>
+      <c r="M107" s="11" t="n">
+        <v>5.4323</v>
+      </c>
+      <c r="N107" s="11" t="n">
+        <v>5.4011</v>
+      </c>
+      <c r="O107" s="11" t="n">
+        <v>5.3703</v>
+      </c>
+      <c r="P107" s="11" t="n">
+        <v>5.3397</v>
+      </c>
+      <c r="Q107" s="11" t="n">
+        <v>5.3041</v>
+      </c>
+      <c r="R107" s="11" t="n">
+        <v>5.2619</v>
+      </c>
+      <c r="S107" s="11" t="n">
+        <v>5.2168</v>
+      </c>
+      <c r="T107" s="11" t="n">
+        <v>5.1716</v>
+      </c>
+      <c r="U107" s="11" t="n">
+        <v>5.1283</v>
+      </c>
+      <c r="V107" s="11" t="n">
+        <v>5.0886</v>
+      </c>
+      <c r="W107" s="11" t="n">
+        <v>5.0539</v>
+      </c>
+      <c r="X107" s="11" t="n">
+        <v>5.0251</v>
+      </c>
+      <c r="Y107" s="11" t="n">
+        <v>5.0031</v>
+      </c>
+      <c r="Z107" s="11" t="n">
+        <v>4.9885</v>
+      </c>
+      <c r="AA107" s="11" t="n">
+        <v>4.9821</v>
+      </c>
+      <c r="AB107" s="11" t="n">
+        <v>4.9841</v>
+      </c>
+      <c r="AC107" s="11" t="n">
+        <v>4.9936</v>
+      </c>
+      <c r="AD107" s="11" t="n">
+        <v>5.0081</v>
+      </c>
+      <c r="AE107" s="11" t="n">
+        <v>5.0262</v>
+      </c>
+      <c r="AF107" s="11" t="n">
+        <v>5.0469</v>
+      </c>
+      <c r="AG107" s="11" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="AH107" s="11" t="n">
+        <v>5.0918</v>
+      </c>
+      <c r="AI107" s="11" t="n">
+        <v>5.1145</v>
+      </c>
+      <c r="AJ107" s="11" t="n">
+        <v>5.1365</v>
+      </c>
+      <c r="AK107" s="11" t="n">
+        <v>5.1571</v>
+      </c>
+      <c r="AL107" s="11" t="n">
+        <v>5.1759</v>
+      </c>
+      <c r="AM107" s="11" t="n">
+        <v>5.1924</v>
+      </c>
+      <c r="AN107" s="11" t="n">
+        <v>5.2062</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>2.6633</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>2.6104</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>2.4548</v>
+      </c>
+      <c r="G108" s="11" t="n">
+        <v>2.5198</v>
+      </c>
+      <c r="H108" s="11" t="n">
+        <v>2.6147</v>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>2.5762</v>
+      </c>
+      <c r="J108" s="11" t="n">
+        <v>2.4044</v>
+      </c>
+      <c r="K108" s="11" t="n">
+        <v>2.2088</v>
+      </c>
+      <c r="L108" s="11" t="n">
+        <v>2.0735</v>
+      </c>
+      <c r="M108" s="11" t="n">
+        <v>1.9985</v>
+      </c>
+      <c r="N108" s="11" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="O108" s="11" t="n">
+        <v>2.0294</v>
+      </c>
+      <c r="P108" s="11" t="n">
+        <v>2.1353</v>
+      </c>
+      <c r="Q108" s="11" t="n">
+        <v>2.1615</v>
+      </c>
+      <c r="R108" s="11" t="n">
+        <v>2.1846</v>
+      </c>
+      <c r="S108" s="11" t="n">
+        <v>2.2047</v>
+      </c>
+      <c r="T108" s="11" t="n">
+        <v>2.2217</v>
+      </c>
+      <c r="U108" s="11" t="n">
+        <v>2.2356</v>
+      </c>
+      <c r="V108" s="11" t="n">
+        <v>2.2465</v>
+      </c>
+      <c r="W108" s="11" t="n">
+        <v>2.2543</v>
+      </c>
+      <c r="X108" s="11" t="n">
+        <v>2.2591</v>
+      </c>
+      <c r="Y108" s="11" t="n">
+        <v>2.2608</v>
+      </c>
+      <c r="Z108" s="11" t="n">
+        <v>2.2594</v>
+      </c>
+      <c r="AA108" s="11" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AB108" s="11" t="n">
+        <v>2.2475</v>
+      </c>
+      <c r="AC108" s="11" t="n">
+        <v>2.2535</v>
+      </c>
+      <c r="AD108" s="11" t="n">
+        <v>2.2588</v>
+      </c>
+      <c r="AE108" s="11" t="n">
+        <v>2.2632</v>
+      </c>
+      <c r="AF108" s="11" t="n">
+        <v>2.2668</v>
+      </c>
+      <c r="AG108" s="11" t="n">
+        <v>2.2697</v>
+      </c>
+      <c r="AH108" s="11" t="n">
+        <v>2.2717</v>
+      </c>
+      <c r="AI108" s="11" t="n">
+        <v>2.2729</v>
+      </c>
+      <c r="AJ108" s="11" t="n">
+        <v>2.2733</v>
+      </c>
+      <c r="AK108" s="11" t="n">
+        <v>2.2729</v>
+      </c>
+      <c r="AL108" s="11" t="n">
+        <v>2.2717</v>
+      </c>
+      <c r="AM108" s="11" t="n">
+        <v>2.2697</v>
+      </c>
+      <c r="AN108" s="11" t="n">
+        <v>2.2668</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>2.6633</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>2.6698</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="G109" s="11" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>2.5578</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>2.5676</v>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>2.5565</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>2.5201</v>
+      </c>
+      <c r="L109" s="11" t="n">
+        <v>2.4721</v>
+      </c>
+      <c r="M109" s="11" t="n">
+        <v>2.4231</v>
+      </c>
+      <c r="N109" s="11" t="n">
+        <v>2.3794</v>
+      </c>
+      <c r="O109" s="11" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="P109" s="11" t="n">
+        <v>2.3227</v>
+      </c>
+      <c r="Q109" s="11" t="n">
+        <v>2.3093</v>
+      </c>
+      <c r="R109" s="11" t="n">
+        <v>2.2996</v>
+      </c>
+      <c r="S109" s="11" t="n">
+        <v>2.2927</v>
+      </c>
+      <c r="T109" s="11" t="n">
+        <v>2.2877</v>
+      </c>
+      <c r="U109" s="11" t="n">
+        <v>2.2842</v>
+      </c>
+      <c r="V109" s="11" t="n">
+        <v>2.2819</v>
+      </c>
+      <c r="W109" s="11" t="n">
+        <v>2.2802</v>
+      </c>
+      <c r="X109" s="11" t="n">
+        <v>2.279</v>
+      </c>
+      <c r="Y109" s="11" t="n">
+        <v>2.2781</v>
+      </c>
+      <c r="Z109" s="11" t="n">
+        <v>2.2773</v>
+      </c>
+      <c r="AA109" s="11" t="n">
+        <v>2.2765</v>
+      </c>
+      <c r="AB109" s="11" t="n">
+        <v>2.2754</v>
+      </c>
+      <c r="AC109" s="11" t="n">
+        <v>2.2744</v>
+      </c>
+      <c r="AD109" s="11" t="n">
+        <v>2.2737</v>
+      </c>
+      <c r="AE109" s="11" t="n">
+        <v>2.2733</v>
+      </c>
+      <c r="AF109" s="11" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="AG109" s="11" t="n">
+        <v>2.2728</v>
+      </c>
+      <c r="AH109" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="AI109" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="AJ109" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="AK109" s="11" t="n">
+        <v>2.2728</v>
+      </c>
+      <c r="AL109" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="AM109" s="11" t="n">
+        <v>2.2727</v>
+      </c>
+      <c r="AN109" s="11" t="n">
+        <v>2.2726</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN103"/>
+  <autoFilter ref="A1:AN109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45778,7 +46616,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-13  (17 daily snapshots, 102 curve rows)</t>
+          <t>2026-08-28 to 2026-09-14  (18 daily snapshots, 108 curve rows)</t>
         </is>
       </c>
     </row>
@@ -45850,7 +46688,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-10  (20 rows)</t>
+          <t>2026-08-22 to 2026-09-13  (23 rows)</t>
         </is>
       </c>
     </row>
@@ -45886,7 +46724,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14 15:54 local</t>
+          <t>2026-09-14 20:20 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$24</f>
+              <f>'Daily Index'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$24</f>
+              <f>'Daily Index'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$24</f>
+              <f>'Daily Index'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$24</f>
+              <f>'Daily Index'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$24</f>
+              <f>'Daily Index'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$24</f>
+              <f>'Daily Index'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1640,8 +1640,34 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1.6379</v>
+      </c>
+      <c r="E25" s="4">
+        <f>IF(OR(B25="",B24=""),"",B25/B24-1)</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>IF(OR(C25="",C24=""),"",C25/C24-1)</f>
+        <v/>
+      </c>
+      <c r="G25" s="4">
+        <f>IF(OR(D25="",D24=""),"",D25/D24-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:G25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46688,7 +46714,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-13  (23 rows)</t>
+          <t>2026-08-22 to 2026-09-14  (24 rows)</t>
         </is>
       </c>
     </row>
@@ -46724,7 +46750,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14 20:20 local</t>
+          <t>2026-09-15 14:20 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
   </definedNames>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$24</f>
+              <f>'GPU Rental'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$24</f>
+              <f>'GPU Rental'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$24</f>
+              <f>'GPU Rental'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$24</f>
+              <f>'GPU Rental'!$E$2:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$24</f>
+              <f>'GPU Rental'!$F$2:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$24</f>
+              <f>'GPU Rental'!$G$2:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$24</f>
+              <f>'GPU Rental'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$24</f>
+              <f>'GPU Rental'!$H$2:$H$25</f>
             </numRef>
           </val>
         </ser>
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2989,8 +2989,62 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" s="4">
+        <f>IF(OR(B25="",B24=""),"",B25/B24-1)</f>
+        <v/>
+      </c>
+      <c r="J25" s="4">
+        <f>IF(OR(C25="",C24=""),"",C25/C24-1)</f>
+        <v/>
+      </c>
+      <c r="K25" s="4">
+        <f>IF(OR(D25="",D24=""),"",D25/D24-1)</f>
+        <v/>
+      </c>
+      <c r="L25" s="4">
+        <f>IF(OR(E25="",E24=""),"",E25/E24-1)</f>
+        <v/>
+      </c>
+      <c r="M25" s="4">
+        <f>IF(OR(F25="",F24=""),"",F25/F24-1)</f>
+        <v/>
+      </c>
+      <c r="N25" s="4">
+        <f>IF(OR(G25="",G24=""),"",G25/G24-1)</f>
+        <v/>
+      </c>
+      <c r="O25" s="4">
+        <f>IF(OR(H25="",H24=""),"",H25/H24-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O24"/>
+  <autoFilter ref="A1:O25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3001,7 +3055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN109"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16856,8 +16910,764 @@
         <v>2.2726</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>1.5783</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>1.5799</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>1.6946</v>
+      </c>
+      <c r="G110" s="11" t="n">
+        <v>1.6185</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="I110" s="11" t="n">
+        <v>1.5299</v>
+      </c>
+      <c r="J110" s="11" t="n">
+        <v>1.4862</v>
+      </c>
+      <c r="K110" s="11" t="n">
+        <v>1.4086</v>
+      </c>
+      <c r="L110" s="11" t="n">
+        <v>1.3535</v>
+      </c>
+      <c r="M110" s="11" t="n">
+        <v>1.3208</v>
+      </c>
+      <c r="N110" s="11" t="n">
+        <v>1.3106</v>
+      </c>
+      <c r="O110" s="11" t="n">
+        <v>1.3228</v>
+      </c>
+      <c r="P110" s="11" t="n">
+        <v>1.3575</v>
+      </c>
+      <c r="Q110" s="11" t="n">
+        <v>1.3718</v>
+      </c>
+      <c r="R110" s="11" t="n">
+        <v>1.3823</v>
+      </c>
+      <c r="S110" s="11" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="T110" s="11" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="U110" s="11" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="V110" s="11" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="W110" s="11" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="X110" s="11" t="n">
+        <v>1.3654</v>
+      </c>
+      <c r="Y110" s="11" t="n">
+        <v>1.3493</v>
+      </c>
+      <c r="Z110" s="11" t="n">
+        <v>1.3293</v>
+      </c>
+      <c r="AA110" s="11" t="n">
+        <v>1.3055</v>
+      </c>
+      <c r="AB110" s="11" t="n">
+        <v>1.2779</v>
+      </c>
+      <c r="AC110" s="11" t="n">
+        <v>1.2512</v>
+      </c>
+      <c r="AD110" s="11" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="AE110" s="11" t="n">
+        <v>1.2084</v>
+      </c>
+      <c r="AF110" s="11" t="n">
+        <v>1.1924</v>
+      </c>
+      <c r="AG110" s="11" t="n">
+        <v>1.1799</v>
+      </c>
+      <c r="AH110" s="11" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="AI110" s="11" t="n">
+        <v>1.1657</v>
+      </c>
+      <c r="AJ110" s="11" t="n">
+        <v>1.1639</v>
+      </c>
+      <c r="AK110" s="11" t="n">
+        <v>1.1657</v>
+      </c>
+      <c r="AL110" s="11" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="AM110" s="11" t="n">
+        <v>1.1799</v>
+      </c>
+      <c r="AN110" s="11" t="n">
+        <v>1.1924</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>1.5783</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>1.5958</v>
+      </c>
+      <c r="G111" s="11" t="n">
+        <v>1.6214</v>
+      </c>
+      <c r="H111" s="11" t="n">
+        <v>1.6151</v>
+      </c>
+      <c r="I111" s="11" t="n">
+        <v>1.6024</v>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>1.5867</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>1.5665</v>
+      </c>
+      <c r="L111" s="11" t="n">
+        <v>1.5431</v>
+      </c>
+      <c r="M111" s="11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N111" s="11" t="n">
+        <v>1.4994</v>
+      </c>
+      <c r="O111" s="11" t="n">
+        <v>1.4826</v>
+      </c>
+      <c r="P111" s="11" t="n">
+        <v>1.4706</v>
+      </c>
+      <c r="Q111" s="11" t="n">
+        <v>1.4625</v>
+      </c>
+      <c r="R111" s="11" t="n">
+        <v>1.4564</v>
+      </c>
+      <c r="S111" s="11" t="n">
+        <v>1.4517</v>
+      </c>
+      <c r="T111" s="11" t="n">
+        <v>1.4479</v>
+      </c>
+      <c r="U111" s="11" t="n">
+        <v>1.4446</v>
+      </c>
+      <c r="V111" s="11" t="n">
+        <v>1.4415</v>
+      </c>
+      <c r="W111" s="11" t="n">
+        <v>1.4384</v>
+      </c>
+      <c r="X111" s="11" t="n">
+        <v>1.4351</v>
+      </c>
+      <c r="Y111" s="11" t="n">
+        <v>1.4314</v>
+      </c>
+      <c r="Z111" s="11" t="n">
+        <v>1.4272</v>
+      </c>
+      <c r="AA111" s="11" t="n">
+        <v>1.4225</v>
+      </c>
+      <c r="AB111" s="11" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="AC111" s="11" t="n">
+        <v>1.4109</v>
+      </c>
+      <c r="AD111" s="11" t="n">
+        <v>1.4043</v>
+      </c>
+      <c r="AE111" s="11" t="n">
+        <v>1.3974</v>
+      </c>
+      <c r="AF111" s="11" t="n">
+        <v>1.3904</v>
+      </c>
+      <c r="AG111" s="11" t="n">
+        <v>1.3833</v>
+      </c>
+      <c r="AH111" s="11" t="n">
+        <v>1.3764</v>
+      </c>
+      <c r="AI111" s="11" t="n">
+        <v>1.3697</v>
+      </c>
+      <c r="AJ111" s="11" t="n">
+        <v>1.3632</v>
+      </c>
+      <c r="AK111" s="11" t="n">
+        <v>1.3572</v>
+      </c>
+      <c r="AL111" s="11" t="n">
+        <v>1.3517</v>
+      </c>
+      <c r="AM111" s="11" t="n">
+        <v>1.3466</v>
+      </c>
+      <c r="AN111" s="11" t="n">
+        <v>1.3421</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>5.7325</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>5.692</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>5.8036</v>
+      </c>
+      <c r="G112" s="11" t="n">
+        <v>5.6074</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>5.4157</v>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>5.3175</v>
+      </c>
+      <c r="J112" s="11" t="n">
+        <v>5.3127</v>
+      </c>
+      <c r="K112" s="11" t="n">
+        <v>5.2649</v>
+      </c>
+      <c r="L112" s="11" t="n">
+        <v>5.2146</v>
+      </c>
+      <c r="M112" s="11" t="n">
+        <v>5.1618</v>
+      </c>
+      <c r="N112" s="11" t="n">
+        <v>5.1065</v>
+      </c>
+      <c r="O112" s="11" t="n">
+        <v>5.0487</v>
+      </c>
+      <c r="P112" s="11" t="n">
+        <v>4.9884</v>
+      </c>
+      <c r="Q112" s="11" t="n">
+        <v>4.8085</v>
+      </c>
+      <c r="R112" s="11" t="n">
+        <v>4.6638</v>
+      </c>
+      <c r="S112" s="11" t="n">
+        <v>4.5544</v>
+      </c>
+      <c r="T112" s="11" t="n">
+        <v>4.4802</v>
+      </c>
+      <c r="U112" s="11" t="n">
+        <v>4.4412</v>
+      </c>
+      <c r="V112" s="11" t="n">
+        <v>4.4375</v>
+      </c>
+      <c r="W112" s="11" t="n">
+        <v>4.4691</v>
+      </c>
+      <c r="X112" s="11" t="n">
+        <v>4.5358</v>
+      </c>
+      <c r="Y112" s="11" t="n">
+        <v>4.6379</v>
+      </c>
+      <c r="Z112" s="11" t="n">
+        <v>4.7751</v>
+      </c>
+      <c r="AA112" s="11" t="n">
+        <v>4.9476</v>
+      </c>
+      <c r="AB112" s="11" t="n">
+        <v>5.1554</v>
+      </c>
+      <c r="AC112" s="11" t="n">
+        <v>5.3136</v>
+      </c>
+      <c r="AD112" s="11" t="n">
+        <v>5.4507</v>
+      </c>
+      <c r="AE112" s="11" t="n">
+        <v>5.5668</v>
+      </c>
+      <c r="AF112" s="11" t="n">
+        <v>5.6617</v>
+      </c>
+      <c r="AG112" s="11" t="n">
+        <v>5.7356</v>
+      </c>
+      <c r="AH112" s="11" t="n">
+        <v>5.7883</v>
+      </c>
+      <c r="AI112" s="11" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AJ112" s="11" t="n">
+        <v>5.8305</v>
+      </c>
+      <c r="AK112" s="11" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AL112" s="11" t="n">
+        <v>5.7883</v>
+      </c>
+      <c r="AM112" s="11" t="n">
+        <v>5.7356</v>
+      </c>
+      <c r="AN112" s="11" t="n">
+        <v>5.6617</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>5.7325</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>5.6619</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>5.7177</v>
+      </c>
+      <c r="G113" s="11" t="n">
+        <v>5.7222</v>
+      </c>
+      <c r="H113" s="11" t="n">
+        <v>5.6676</v>
+      </c>
+      <c r="I113" s="11" t="n">
+        <v>5.6058</v>
+      </c>
+      <c r="J113" s="11" t="n">
+        <v>5.5561</v>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>5.5179</v>
+      </c>
+      <c r="L113" s="11" t="n">
+        <v>5.4832</v>
+      </c>
+      <c r="M113" s="11" t="n">
+        <v>5.4504</v>
+      </c>
+      <c r="N113" s="11" t="n">
+        <v>5.4188</v>
+      </c>
+      <c r="O113" s="11" t="n">
+        <v>5.3878</v>
+      </c>
+      <c r="P113" s="11" t="n">
+        <v>5.3571</v>
+      </c>
+      <c r="Q113" s="11" t="n">
+        <v>5.3215</v>
+      </c>
+      <c r="R113" s="11" t="n">
+        <v>5.2795</v>
+      </c>
+      <c r="S113" s="11" t="n">
+        <v>5.2346</v>
+      </c>
+      <c r="T113" s="11" t="n">
+        <v>5.1896</v>
+      </c>
+      <c r="U113" s="11" t="n">
+        <v>5.1466</v>
+      </c>
+      <c r="V113" s="11" t="n">
+        <v>5.1071</v>
+      </c>
+      <c r="W113" s="11" t="n">
+        <v>5.0725</v>
+      </c>
+      <c r="X113" s="11" t="n">
+        <v>5.0439</v>
+      </c>
+      <c r="Y113" s="11" t="n">
+        <v>5.022</v>
+      </c>
+      <c r="Z113" s="11" t="n">
+        <v>5.0075</v>
+      </c>
+      <c r="AA113" s="11" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="AB113" s="11" t="n">
+        <v>5.003</v>
+      </c>
+      <c r="AC113" s="11" t="n">
+        <v>5.0123</v>
+      </c>
+      <c r="AD113" s="11" t="n">
+        <v>5.0266</v>
+      </c>
+      <c r="AE113" s="11" t="n">
+        <v>5.0446</v>
+      </c>
+      <c r="AF113" s="11" t="n">
+        <v>5.065</v>
+      </c>
+      <c r="AG113" s="11" t="n">
+        <v>5.0869</v>
+      </c>
+      <c r="AH113" s="11" t="n">
+        <v>5.1094</v>
+      </c>
+      <c r="AI113" s="11" t="n">
+        <v>5.1319</v>
+      </c>
+      <c r="AJ113" s="11" t="n">
+        <v>5.1536</v>
+      </c>
+      <c r="AK113" s="11" t="n">
+        <v>5.174</v>
+      </c>
+      <c r="AL113" s="11" t="n">
+        <v>5.1926</v>
+      </c>
+      <c r="AM113" s="11" t="n">
+        <v>5.2089</v>
+      </c>
+      <c r="AN113" s="11" t="n">
+        <v>5.2226</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>forward_rate</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>2.6629</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>2.6084</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>2.4712</v>
+      </c>
+      <c r="G114" s="11" t="n">
+        <v>2.5299</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>2.6199</v>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>2.5821</v>
+      </c>
+      <c r="J114" s="11" t="n">
+        <v>2.4166</v>
+      </c>
+      <c r="K114" s="11" t="n">
+        <v>2.2281</v>
+      </c>
+      <c r="L114" s="11" t="n">
+        <v>2.0975</v>
+      </c>
+      <c r="M114" s="11" t="n">
+        <v>2.0248</v>
+      </c>
+      <c r="N114" s="11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O114" s="11" t="n">
+        <v>2.053</v>
+      </c>
+      <c r="P114" s="11" t="n">
+        <v>2.1539</v>
+      </c>
+      <c r="Q114" s="11" t="n">
+        <v>2.1763</v>
+      </c>
+      <c r="R114" s="11" t="n">
+        <v>2.1964</v>
+      </c>
+      <c r="S114" s="11" t="n">
+        <v>2.2141</v>
+      </c>
+      <c r="T114" s="11" t="n">
+        <v>2.2294</v>
+      </c>
+      <c r="U114" s="11" t="n">
+        <v>2.2423</v>
+      </c>
+      <c r="V114" s="11" t="n">
+        <v>2.2527</v>
+      </c>
+      <c r="W114" s="11" t="n">
+        <v>2.2608</v>
+      </c>
+      <c r="X114" s="11" t="n">
+        <v>2.2665</v>
+      </c>
+      <c r="Y114" s="11" t="n">
+        <v>2.2698</v>
+      </c>
+      <c r="Z114" s="11" t="n">
+        <v>2.2707</v>
+      </c>
+      <c r="AA114" s="11" t="n">
+        <v>2.2692</v>
+      </c>
+      <c r="AB114" s="11" t="n">
+        <v>2.2653</v>
+      </c>
+      <c r="AC114" s="11" t="n">
+        <v>2.2738</v>
+      </c>
+      <c r="AD114" s="11" t="n">
+        <v>2.2811</v>
+      </c>
+      <c r="AE114" s="11" t="n">
+        <v>2.2873</v>
+      </c>
+      <c r="AF114" s="11" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="AG114" s="11" t="n">
+        <v>2.2963</v>
+      </c>
+      <c r="AH114" s="11" t="n">
+        <v>2.2991</v>
+      </c>
+      <c r="AI114" s="11" t="n">
+        <v>2.3008</v>
+      </c>
+      <c r="AJ114" s="11" t="n">
+        <v>2.3013</v>
+      </c>
+      <c r="AK114" s="11" t="n">
+        <v>2.3008</v>
+      </c>
+      <c r="AL114" s="11" t="n">
+        <v>2.2991</v>
+      </c>
+      <c r="AM114" s="11" t="n">
+        <v>2.2963</v>
+      </c>
+      <c r="AN114" s="11" t="n">
+        <v>2.2923</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>term_rate</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>2.6629</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>2.6606</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>2.5921</v>
+      </c>
+      <c r="G115" s="11" t="n">
+        <v>2.5561</v>
+      </c>
+      <c r="H115" s="11" t="n">
+        <v>2.5635</v>
+      </c>
+      <c r="I115" s="11" t="n">
+        <v>2.5731</v>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>2.5626</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>2.5276</v>
+      </c>
+      <c r="L115" s="11" t="n">
+        <v>2.4814</v>
+      </c>
+      <c r="M115" s="11" t="n">
+        <v>2.4342</v>
+      </c>
+      <c r="N115" s="11" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="O115" s="11" t="n">
+        <v>2.3588</v>
+      </c>
+      <c r="P115" s="11" t="n">
+        <v>2.3371</v>
+      </c>
+      <c r="Q115" s="11" t="n">
+        <v>2.3239</v>
+      </c>
+      <c r="R115" s="11" t="n">
+        <v>2.3141</v>
+      </c>
+      <c r="S115" s="11" t="n">
+        <v>2.3068</v>
+      </c>
+      <c r="T115" s="11" t="n">
+        <v>2.3015</v>
+      </c>
+      <c r="U115" s="11" t="n">
+        <v>2.2977</v>
+      </c>
+      <c r="V115" s="11" t="n">
+        <v>2.2949</v>
+      </c>
+      <c r="W115" s="11" t="n">
+        <v>2.2929</v>
+      </c>
+      <c r="X115" s="11" t="n">
+        <v>2.2915</v>
+      </c>
+      <c r="Y115" s="11" t="n">
+        <v>2.2904</v>
+      </c>
+      <c r="Z115" s="11" t="n">
+        <v>2.2895</v>
+      </c>
+      <c r="AA115" s="11" t="n">
+        <v>2.2886</v>
+      </c>
+      <c r="AB115" s="11" t="n">
+        <v>2.2877</v>
+      </c>
+      <c r="AC115" s="11" t="n">
+        <v>2.287</v>
+      </c>
+      <c r="AD115" s="11" t="n">
+        <v>2.2866</v>
+      </c>
+      <c r="AE115" s="11" t="n">
+        <v>2.2866</v>
+      </c>
+      <c r="AF115" s="11" t="n">
+        <v>2.2867</v>
+      </c>
+      <c r="AG115" s="11" t="n">
+        <v>2.2869</v>
+      </c>
+      <c r="AH115" s="11" t="n">
+        <v>2.2873</v>
+      </c>
+      <c r="AI115" s="11" t="n">
+        <v>2.2877</v>
+      </c>
+      <c r="AJ115" s="11" t="n">
+        <v>2.2881</v>
+      </c>
+      <c r="AK115" s="11" t="n">
+        <v>2.2885</v>
+      </c>
+      <c r="AL115" s="11" t="n">
+        <v>2.2889</v>
+      </c>
+      <c r="AM115" s="11" t="n">
+        <v>2.2891</v>
+      </c>
+      <c r="AN115" s="11" t="n">
+        <v>2.2893</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN109"/>
+  <autoFilter ref="A1:AN115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46642,7 +47452,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-14  (18 daily snapshots, 108 curve rows)</t>
+          <t>2026-08-28 to 2026-09-15  (19 daily snapshots, 114 curve rows)</t>
         </is>
       </c>
     </row>
@@ -46738,7 +47548,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-14  (23 rows)</t>
+          <t>2026-08-23 to 2026-09-15  (24 rows)</t>
         </is>
       </c>
     </row>
@@ -46750,7 +47560,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 14:20 local</t>
+          <t>2026-09-15 19:44 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$25</f>
+              <f>'Daily Index'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$25</f>
+              <f>'Daily Index'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$25</f>
+              <f>'Daily Index'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$25</f>
+              <f>'Daily Index'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$25</f>
+              <f>'Daily Index'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$25</f>
+              <f>'Daily Index'!$D$2:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$25</f>
+              <f>'GPU Rental'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$25</f>
+              <f>'GPU Rental'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$25</f>
+              <f>'GPU Rental'!$D$2:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$25</f>
+              <f>'GPU Rental'!$E$2:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$25</f>
+              <f>'GPU Rental'!$F$2:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$25</f>
+              <f>'GPU Rental'!$G$2:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$25</f>
+              <f>'GPU Rental'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$25</f>
+              <f>'GPU Rental'!$H$2:$H$26</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1666,8 +1666,34 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>0.9527</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="E26" s="4">
+        <f>IF(OR(B26="",B25=""),"",B26/B25-1)</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>IF(OR(C26="",C25=""),"",C26/C25-1)</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(OR(D26="",D25=""),"",D26/D25-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1678,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2955,7 +2981,7 @@
         <v>5.72</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>3.75</v>
@@ -3009,7 +3035,7 @@
         <v>5.73</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>3.75</v>
@@ -3043,8 +3069,62 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I26" s="4">
+        <f>IF(OR(B26="",B25=""),"",B26/B25-1)</f>
+        <v/>
+      </c>
+      <c r="J26" s="4">
+        <f>IF(OR(C26="",C25=""),"",C26/C25-1)</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>IF(OR(D26="",D25=""),"",D26/D25-1)</f>
+        <v/>
+      </c>
+      <c r="L26" s="4">
+        <f>IF(OR(E26="",E25=""),"",E26/E25-1)</f>
+        <v/>
+      </c>
+      <c r="M26" s="4">
+        <f>IF(OR(F26="",F25=""),"",F26/F25-1)</f>
+        <v/>
+      </c>
+      <c r="N26" s="4">
+        <f>IF(OR(G26="",G25=""),"",G26/G25-1)</f>
+        <v/>
+      </c>
+      <c r="O26" s="4">
+        <f>IF(OR(H26="",H25=""),"",H26/H25-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O25"/>
+  <autoFilter ref="A1:O26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46985,7 +47065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -47264,7 +47344,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/forward_curve_raw - full 145-tenor payload, one file per day, never deleted</t>
+          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/forward_curve_raw - full payload as published (145 tenors under the old page), one file per day, never deleted; undated_*.json = curves kept verbatim that could not be dated</t>
         </is>
       </c>
     </row>
@@ -47435,132 +47515,108 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Archive (fc)</t>
+          <t>Archive (ramp_adoption)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/forward_curve.csv</t>
+          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/ramp_adoption.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Span (fc)</t>
+          <t>Span (ramp_adoption)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 to 2026-09-15  (19 daily snapshots, 114 curve rows)</t>
+          <t>2023-01-01 to 2026-08-01  (44 months, 784 rows)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Archive (ramp_adoption)</t>
+          <t>Archive (ramp_spend)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/ramp_adoption.csv</t>
+          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/ramp_spend.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Span (ramp_adoption)</t>
+          <t>Span (ramp_spend)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2023-01-01 to 2026-08-01  (44 months, 784 rows)</t>
+          <t>2023-08-01 to 2026-08-01  (37 months, 486 rows)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Archive (ramp_spend)</t>
+          <t>Archive (llm)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/ramp_spend.csv</t>
+          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/llm_token_index.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Span (ramp_spend)</t>
+          <t>Span (llm)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-08-01 to 2026-08-01  (37 months, 486 rows)</t>
+          <t>2026-08-22 to 2026-09-15  (25 rows)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Archive (llm)</t>
+          <t>Archive (gpu)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/llm_token_index.csv</t>
+          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/gpu_rental_index.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Span (llm)</t>
+          <t>Span (gpu)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-14  (24 rows)</t>
+          <t>2026-08-23 to 2026-09-16  (25 rows)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Archive (gpu)</t>
+          <t>Last updated</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/home/runner/work/silicon-data-tracker/silicon-data-tracker/data/gpu_rental_index.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Span (gpu)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-08-23 to 2026-09-15  (24 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Last updated</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-15 19:44 local</t>
+          <t>2026-09-17 04:17 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$26</f>
+              <f>'Daily Index'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$26</f>
+              <f>'Daily Index'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$26</f>
+              <f>'Daily Index'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$26</f>
+              <f>'Daily Index'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$26</f>
+              <f>'Daily Index'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$26</f>
+              <f>'Daily Index'!$D$2:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1692,8 +1692,32 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n">
+        <v>1.6459</v>
+      </c>
+      <c r="E27" s="4">
+        <f>IF(OR(B27="",B26=""),"",B27/B26-1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>IF(OR(C27="",C26=""),"",C27/C26-1)</f>
+        <v/>
+      </c>
+      <c r="G27" s="4">
+        <f>IF(OR(D27="",D26=""),"",D27/D26-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47580,7 +47604,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-15  (25 rows)</t>
+          <t>2026-08-22 to 2026-09-16  (26 rows)</t>
         </is>
       </c>
     </row>
@@ -47616,7 +47640,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-17 04:17 local</t>
+          <t>2026-09-17 14:19 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -187,188 +187,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Silicon Data LLM Token Expenditure Indices</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Daily Index'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Daily Index'!$B$2:$B$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Daily Index'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Daily Index'!$C$2:$C$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Daily Index'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Daily Index'!$D$2:$D$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Date</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD / M tokens</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Silicon Data GPU Rental Price Indices</a:t>
             </a:r>
           </a:p>
@@ -401,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$26</f>
+              <f>'GPU Rental'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$26</f>
+              <f>'GPU Rental'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$26</f>
+              <f>'GPU Rental'!$D$2:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +315,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$26</f>
+              <f>'GPU Rental'!$E$2:$E$27</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +347,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$26</f>
+              <f>'GPU Rental'!$F$2:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$26</f>
+              <f>'GPU Rental'!$G$2:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +411,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$26</f>
+              <f>'GPU Rental'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$26</f>
+              <f>'GPU Rental'!$H$2:$H$27</f>
             </numRef>
           </val>
         </ser>
@@ -686,28 +504,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="11520000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1728,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3147,8 +2943,62 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I27" s="4">
+        <f>IF(OR(B27="",B26=""),"",B27/B26-1)</f>
+        <v/>
+      </c>
+      <c r="J27" s="4">
+        <f>IF(OR(C27="",C26=""),"",C27/C26-1)</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>IF(OR(D27="",D26=""),"",D27/D26-1)</f>
+        <v/>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(OR(E27="",E26=""),"",E27/E26-1)</f>
+        <v/>
+      </c>
+      <c r="M27" s="4">
+        <f>IF(OR(F27="",F26=""),"",F27/F26-1)</f>
+        <v/>
+      </c>
+      <c r="N27" s="4">
+        <f>IF(OR(G27="",G26=""),"",G27/G26-1)</f>
+        <v/>
+      </c>
+      <c r="O27" s="4">
+        <f>IF(OR(H27="",H26=""),"",H27/H26-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O26"/>
+  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47604,7 +47454,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-16  (26 rows)</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -47628,7 +47478,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-16  (25 rows)</t>
+          <t>2026-08-23 to 2026-09-17  (26 rows)</t>
         </is>
       </c>
     </row>
@@ -47640,7 +47490,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-17 14:19 local</t>
+          <t>2026-09-17 19:45 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -176,6 +175,188 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Silicon Data LLM Token Expenditure Indices</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Daily Index'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Daily Index'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Daily Index'!$B$2:$B$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Daily Index'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Daily Index'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Daily Index'!$C$2:$C$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Daily Index'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Daily Index'!$A$2:$A$27</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Daily Index'!$D$2:$D$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD / M tokens</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -509,6 +690,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1495,7 +1698,9 @@
       <c r="B27" s="11" t="n">
         <v>0.9485</v>
       </c>
-      <c r="C27" s="11" t="n"/>
+      <c r="C27" s="11" t="n">
+        <v>0.5086000000000001</v>
+      </c>
       <c r="D27" s="11" t="n">
         <v>1.6459</v>
       </c>
@@ -47454,7 +47659,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>2026-08-22 to 2026-09-16  (26 rows)</t>
         </is>
       </c>
     </row>
@@ -47490,7 +47695,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-17 19:45 local</t>
+          <t>2026-09-18 05:55 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$27</f>
+              <f>'GPU Rental'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$27</f>
+              <f>'GPU Rental'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$27</f>
+              <f>'GPU Rental'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$27</f>
+              <f>'GPU Rental'!$E$2:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$27</f>
+              <f>'GPU Rental'!$F$2:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$27</f>
+              <f>'GPU Rental'!$G$2:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$27</f>
+              <f>'GPU Rental'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$27</f>
+              <f>'GPU Rental'!$H$2:$H$28</f>
             </numRef>
           </val>
         </ser>
@@ -1729,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3202,8 +3203,62 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" s="4">
+        <f>IF(OR(B28="",B27=""),"",B28/B27-1)</f>
+        <v/>
+      </c>
+      <c r="J28" s="4">
+        <f>IF(OR(C28="",C27=""),"",C28/C27-1)</f>
+        <v/>
+      </c>
+      <c r="K28" s="4">
+        <f>IF(OR(D28="",D27=""),"",D28/D27-1)</f>
+        <v/>
+      </c>
+      <c r="L28" s="4">
+        <f>IF(OR(E28="",E27=""),"",E28/E27-1)</f>
+        <v/>
+      </c>
+      <c r="M28" s="4">
+        <f>IF(OR(F28="",F27=""),"",F28/F27-1)</f>
+        <v/>
+      </c>
+      <c r="N28" s="4">
+        <f>IF(OR(G28="",G27=""),"",G28/G27-1)</f>
+        <v/>
+      </c>
+      <c r="O28" s="4">
+        <f>IF(OR(H28="",H27=""),"",H28/H27-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O27"/>
+  <autoFilter ref="A1:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47683,7 +47738,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-17  (26 rows)</t>
+          <t>2026-08-23 to 2026-09-18  (27 rows)</t>
         </is>
       </c>
     </row>
@@ -47695,7 +47750,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-18 05:55 local</t>
+          <t>2026-09-18 19:04 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
+              <f>'Daily Index'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$27</f>
+              <f>'Daily Index'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
+              <f>'Daily Index'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$27</f>
+              <f>'Daily Index'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$27</f>
+              <f>'Daily Index'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$27</f>
+              <f>'Daily Index'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1718,8 +1718,34 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>0.9550999999999999</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1.7234</v>
+      </c>
+      <c r="E28" s="4">
+        <f>IF(OR(B28="",B27=""),"",B28/B27-1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f>IF(OR(C28="",C27=""),"",C28/C27-1)</f>
+        <v/>
+      </c>
+      <c r="G28" s="4">
+        <f>IF(OR(D28="",D27=""),"",D28/D27-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47714,7 +47740,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-16  (26 rows)</t>
+          <t>2026-08-22 to 2026-09-17  (27 rows)</t>
         </is>
       </c>
     </row>
@@ -47750,7 +47776,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:04 local</t>
+          <t>2026-09-19 05:53 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$28</f>
+              <f>'GPU Rental'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$28</f>
+              <f>'GPU Rental'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$28</f>
+              <f>'GPU Rental'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$28</f>
+              <f>'GPU Rental'!$E$2:$E$29</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$28</f>
+              <f>'GPU Rental'!$F$2:$F$29</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$28</f>
+              <f>'GPU Rental'!$G$2:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$28</f>
+              <f>'GPU Rental'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$28</f>
+              <f>'GPU Rental'!$H$2:$H$29</f>
             </numRef>
           </val>
         </ser>
@@ -1756,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3283,8 +3283,62 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I29" s="4">
+        <f>IF(OR(B29="",B28=""),"",B29/B28-1)</f>
+        <v/>
+      </c>
+      <c r="J29" s="4">
+        <f>IF(OR(C29="",C28=""),"",C29/C28-1)</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>IF(OR(D29="",D28=""),"",D29/D28-1)</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(OR(E29="",E28=""),"",E29/E28-1)</f>
+        <v/>
+      </c>
+      <c r="M29" s="4">
+        <f>IF(OR(F29="",F28=""),"",F29/F28-1)</f>
+        <v/>
+      </c>
+      <c r="N29" s="4">
+        <f>IF(OR(G29="",G28=""),"",G29/G28-1)</f>
+        <v/>
+      </c>
+      <c r="O29" s="4">
+        <f>IF(OR(H29="",H28=""),"",H29/H28-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O28"/>
+  <autoFilter ref="A1:O29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47764,7 +47818,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-18  (27 rows)</t>
+          <t>2026-08-23 to 2026-09-19  (28 rows)</t>
         </is>
       </c>
     </row>
@@ -47776,7 +47830,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19 05:53 local</t>
+          <t>2026-09-19 18:38 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$28</f>
+              <f>'Daily Index'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$28</f>
+              <f>'Daily Index'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$28</f>
+              <f>'Daily Index'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$28</f>
+              <f>'Daily Index'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$28</f>
+              <f>'Daily Index'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$28</f>
+              <f>'Daily Index'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1744,8 +1744,34 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1.8476</v>
+      </c>
+      <c r="E29" s="4">
+        <f>IF(OR(B29="",B28=""),"",B29/B28-1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f>IF(OR(C29="",C28=""),"",C29/C28-1)</f>
+        <v/>
+      </c>
+      <c r="G29" s="4">
+        <f>IF(OR(D29="",D28=""),"",D29/D28-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47794,7 +47820,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-17  (27 rows)</t>
+          <t>2026-08-22 to 2026-09-18  (28 rows)</t>
         </is>
       </c>
     </row>
@@ -47830,7 +47856,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19 18:38 local</t>
+          <t>2026-09-20 06:17 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$29</f>
+              <f>'Daily Index'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$29</f>
+              <f>'Daily Index'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$29</f>
+              <f>'Daily Index'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$29</f>
+              <f>'Daily Index'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$29</f>
+              <f>'Daily Index'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$29</f>
+              <f>'Daily Index'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$29</f>
+              <f>'GPU Rental'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$29</f>
+              <f>'GPU Rental'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$29</f>
+              <f>'GPU Rental'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$29</f>
+              <f>'GPU Rental'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$29</f>
+              <f>'GPU Rental'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$29</f>
+              <f>'GPU Rental'!$G$2:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$29</f>
+              <f>'GPU Rental'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$29</f>
+              <f>'GPU Rental'!$H$2:$H$30</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1770,8 +1770,34 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>1.0088</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1.8638</v>
+      </c>
+      <c r="E30" s="4">
+        <f>IF(OR(B30="",B29=""),"",B30/B29-1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f>IF(OR(C30="",C29=""),"",C30/C29-1)</f>
+        <v/>
+      </c>
+      <c r="G30" s="4">
+        <f>IF(OR(D30="",D29=""),"",D30/D29-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1782,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3363,8 +3389,62 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I30" s="4">
+        <f>IF(OR(B30="",B29=""),"",B30/B29-1)</f>
+        <v/>
+      </c>
+      <c r="J30" s="4">
+        <f>IF(OR(C30="",C29=""),"",C30/C29-1)</f>
+        <v/>
+      </c>
+      <c r="K30" s="4">
+        <f>IF(OR(D30="",D29=""),"",D30/D29-1)</f>
+        <v/>
+      </c>
+      <c r="L30" s="4">
+        <f>IF(OR(E30="",E29=""),"",E30/E29-1)</f>
+        <v/>
+      </c>
+      <c r="M30" s="4">
+        <f>IF(OR(F30="",F29=""),"",F30/F29-1)</f>
+        <v/>
+      </c>
+      <c r="N30" s="4">
+        <f>IF(OR(G30="",G29=""),"",G30/G29-1)</f>
+        <v/>
+      </c>
+      <c r="O30" s="4">
+        <f>IF(OR(H30="",H29=""),"",H30/H29-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47820,7 +47900,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-18  (28 rows)</t>
+          <t>2026-08-22 to 2026-09-19  (29 rows)</t>
         </is>
       </c>
     </row>
@@ -47844,7 +47924,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-19  (28 rows)</t>
+          <t>2026-08-23 to 2026-09-20  (29 rows)</t>
         </is>
       </c>
     </row>
@@ -47856,7 +47936,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-20 06:17 local</t>
+          <t>2026-09-20 18:52 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$30</f>
+              <f>'Daily Index'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$30</f>
+              <f>'Daily Index'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$30</f>
+              <f>'Daily Index'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$30</f>
+              <f>'Daily Index'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$30</f>
+              <f>'Daily Index'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$30</f>
+              <f>'Daily Index'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$30</f>
+              <f>'GPU Rental'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$30</f>
+              <f>'GPU Rental'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$30</f>
+              <f>'GPU Rental'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$30</f>
+              <f>'GPU Rental'!$E$2:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$30</f>
+              <f>'GPU Rental'!$F$2:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$30</f>
+              <f>'GPU Rental'!$G$2:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$30</f>
+              <f>'GPU Rental'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$30</f>
+              <f>'GPU Rental'!$H$2:$H$31</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1796,8 +1796,34 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1.9001</v>
+      </c>
+      <c r="E31" s="4">
+        <f>IF(OR(B31="",B30=""),"",B31/B30-1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f>IF(OR(C31="",C30=""),"",C31/C30-1)</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>IF(OR(D31="",D30=""),"",D31/D30-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1808,7 +1834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3443,8 +3469,58 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I31" s="4">
+        <f>IF(OR(B31="",B30=""),"",B31/B30-1)</f>
+        <v/>
+      </c>
+      <c r="J31" s="4">
+        <f>IF(OR(C31="",C30=""),"",C31/C30-1)</f>
+        <v/>
+      </c>
+      <c r="K31" s="4">
+        <f>IF(OR(D31="",D30=""),"",D31/D30-1)</f>
+        <v/>
+      </c>
+      <c r="L31" s="4">
+        <f>IF(OR(E31="",E30=""),"",E31/E30-1)</f>
+        <v/>
+      </c>
+      <c r="M31" s="4">
+        <f>IF(OR(F31="",F30=""),"",F31/F30-1)</f>
+        <v/>
+      </c>
+      <c r="N31" s="4">
+        <f>IF(OR(G31="",G30=""),"",G31/G30-1)</f>
+        <v/>
+      </c>
+      <c r="O31" s="4">
+        <f>IF(OR(H31="",H30=""),"",H31/H30-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47900,7 +47976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-19  (29 rows)</t>
+          <t>2026-08-22 to 2026-09-20  (30 rows)</t>
         </is>
       </c>
     </row>
@@ -47924,7 +48000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-20  (29 rows)</t>
+          <t>2026-08-23 to 2026-09-21  (30 rows)</t>
         </is>
       </c>
     </row>
@@ -47936,7 +48012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-20 18:52 local</t>
+          <t>2026-09-21 15:55 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3483,7 +3482,9 @@
       <c r="E31" s="5" t="n">
         <v>2.62</v>
       </c>
-      <c r="F31" s="5" t="n"/>
+      <c r="F31" s="5" t="n">
+        <v>5.74</v>
+      </c>
       <c r="G31" s="5" t="n">
         <v>7.17</v>
       </c>
@@ -48012,7 +48013,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 15:55 local</t>
+          <t>2026-09-21 20:27 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -3472,7 +3472,9 @@
       <c r="A31" s="10" t="n">
         <v>46286</v>
       </c>
-      <c r="B31" s="5" t="n"/>
+      <c r="B31" s="5" t="n">
+        <v>2.6</v>
+      </c>
       <c r="C31" s="5" t="n">
         <v>1.57</v>
       </c>
@@ -48013,7 +48015,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 20:27 local</t>
+          <t>2026-09-22 06:14 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -218,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$31</f>
+              <f>'Daily Index'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$31</f>
+              <f>'Daily Index'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -250,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$31</f>
+              <f>'Daily Index'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$31</f>
+              <f>'Daily Index'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$31</f>
+              <f>'Daily Index'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$31</f>
+              <f>'Daily Index'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$31</f>
+              <f>'GPU Rental'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$31</f>
+              <f>'GPU Rental'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$31</f>
+              <f>'GPU Rental'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$31</f>
+              <f>'GPU Rental'!$E$2:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$31</f>
+              <f>'GPU Rental'!$F$2:$F$32</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$31</f>
+              <f>'GPU Rental'!$G$2:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$31</f>
+              <f>'GPU Rental'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$31</f>
+              <f>'GPU Rental'!$H$2:$H$32</f>
             </numRef>
           </val>
         </ser>
@@ -1004,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1821,8 +1822,34 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>1.9654</v>
+      </c>
+      <c r="E32" s="4">
+        <f>IF(OR(B32="",B31=""),"",B32/B31-1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>IF(OR(C32="",C31=""),"",C32/C31-1)</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>IF(OR(D32="",D31=""),"",D32/D31-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1833,7 +1860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3522,8 +3549,62 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I32" s="4">
+        <f>IF(OR(B32="",B31=""),"",B32/B31-1)</f>
+        <v/>
+      </c>
+      <c r="J32" s="4">
+        <f>IF(OR(C32="",C31=""),"",C32/C31-1)</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>IF(OR(D32="",D31=""),"",D32/D31-1)</f>
+        <v/>
+      </c>
+      <c r="L32" s="4">
+        <f>IF(OR(E32="",E31=""),"",E32/E31-1)</f>
+        <v/>
+      </c>
+      <c r="M32" s="4">
+        <f>IF(OR(F32="",F31=""),"",F32/F31-1)</f>
+        <v/>
+      </c>
+      <c r="N32" s="4">
+        <f>IF(OR(G32="",G31=""),"",G32/G31-1)</f>
+        <v/>
+      </c>
+      <c r="O32" s="4">
+        <f>IF(OR(H32="",H31=""),"",H32/H31-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O31"/>
+  <autoFilter ref="A1:O32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47979,7 +48060,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-20  (30 rows)</t>
+          <t>2026-08-22 to 2026-09-21  (31 rows)</t>
         </is>
       </c>
     </row>
@@ -48003,7 +48084,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-21  (30 rows)</t>
+          <t>2026-08-23 to 2026-09-22  (31 rows)</t>
         </is>
       </c>
     </row>
@@ -48015,7 +48096,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-22 06:14 local</t>
+          <t>2026-09-22 19:46 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$32</f>
+              <f>'GPU Rental'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$32</f>
+              <f>'GPU Rental'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$32</f>
+              <f>'GPU Rental'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$32</f>
+              <f>'GPU Rental'!$E$2:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$32</f>
+              <f>'GPU Rental'!$F$2:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$32</f>
+              <f>'GPU Rental'!$G$2:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$32</f>
+              <f>'GPU Rental'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$32</f>
+              <f>'GPU Rental'!$H$2:$H$33</f>
             </numRef>
           </val>
         </ser>
@@ -1860,7 +1860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3603,8 +3603,62 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I33" s="4">
+        <f>IF(OR(B33="",B32=""),"",B33/B32-1)</f>
+        <v/>
+      </c>
+      <c r="J33" s="4">
+        <f>IF(OR(C33="",C32=""),"",C33/C32-1)</f>
+        <v/>
+      </c>
+      <c r="K33" s="4">
+        <f>IF(OR(D33="",D32=""),"",D33/D32-1)</f>
+        <v/>
+      </c>
+      <c r="L33" s="4">
+        <f>IF(OR(E33="",E32=""),"",E33/E32-1)</f>
+        <v/>
+      </c>
+      <c r="M33" s="4">
+        <f>IF(OR(F33="",F32=""),"",F33/F32-1)</f>
+        <v/>
+      </c>
+      <c r="N33" s="4">
+        <f>IF(OR(G33="",G32=""),"",G33/G32-1)</f>
+        <v/>
+      </c>
+      <c r="O33" s="4">
+        <f>IF(OR(H33="",H32=""),"",H33/H32-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
+  <autoFilter ref="A1:O33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48084,7 +48138,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-22  (31 rows)</t>
+          <t>2026-08-23 to 2026-09-23  (32 rows)</t>
         </is>
       </c>
     </row>
@@ -48096,7 +48150,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-22 19:46 local</t>
+          <t>2026-09-23 19:43 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$32</f>
+              <f>'Daily Index'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$32</f>
+              <f>'Daily Index'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$32</f>
+              <f>'Daily Index'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$32</f>
+              <f>'Daily Index'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$32</f>
+              <f>'Daily Index'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$32</f>
+              <f>'Daily Index'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1848,8 +1848,34 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>1.9522</v>
+      </c>
+      <c r="E33" s="4">
+        <f>IF(OR(B33="",B32=""),"",B33/B32-1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="4">
+        <f>IF(OR(C33="",C32=""),"",C33/C32-1)</f>
+        <v/>
+      </c>
+      <c r="G33" s="4">
+        <f>IF(OR(D33="",D32=""),"",D33/D32-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48114,7 +48140,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-21  (31 rows)</t>
+          <t>2026-08-22 to 2026-09-22  (32 rows)</t>
         </is>
       </c>
     </row>
@@ -48150,7 +48176,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-23 19:43 local</t>
+          <t>2026-09-24 06:11 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$33</f>
+              <f>'Daily Index'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$33</f>
+              <f>'Daily Index'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$33</f>
+              <f>'Daily Index'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$33</f>
+              <f>'Daily Index'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$33</f>
+              <f>'Daily Index'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$33</f>
+              <f>'Daily Index'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -357,316 +357,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Silicon Data GPU Rental Price Indices</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$B$2:$B$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$C$2:$C$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$D$2:$D$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$E$2:$E$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$F$2:$F$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$G$2:$G$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'GPU Rental'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GPU Rental'!$A$2:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GPU Rental'!$H$2:$H$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Date</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD / hr</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -686,28 +376,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="11520000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1005,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1874,8 +1542,34 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>0.9582000000000001</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>1.9761</v>
+      </c>
+      <c r="E34" s="4">
+        <f>IF(OR(B34="",B33=""),"",B34/B33-1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>IF(OR(C34="",C33=""),"",C34/C33-1)</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>IF(OR(D34="",D33=""),"",D34/D33-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
+  <autoFilter ref="A1:G34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48140,7 +47834,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-22  (32 rows)</t>
+          <t>2026-08-22 to 2026-09-23  (33 rows)</t>
         </is>
       </c>
     </row>
@@ -48164,7 +47858,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-23  (32 rows)</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
@@ -48176,7 +47870,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-24 06:11 local</t>
+          <t>2026-09-24 20:01 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -357,6 +357,316 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Silicon Data GPU Rental Price Indices</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$B$2:$B$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$C$2:$C$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$D$2:$D$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$E$2:$E$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$F$2:$F$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$G$2:$G$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'GPU Rental'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GPU Rental'!$A$2:$A$34</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GPU Rental'!$H$2:$H$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD / hr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -376,6 +686,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1580,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3377,8 +3709,62 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I34" s="4">
+        <f>IF(OR(B34="",B33=""),"",B34/B33-1)</f>
+        <v/>
+      </c>
+      <c r="J34" s="4">
+        <f>IF(OR(C34="",C33=""),"",C34/C33-1)</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>IF(OR(D34="",D33=""),"",D34/D33-1)</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>IF(OR(E34="",E33=""),"",E34/E33-1)</f>
+        <v/>
+      </c>
+      <c r="M34" s="4">
+        <f>IF(OR(F34="",F33=""),"",F34/F33-1)</f>
+        <v/>
+      </c>
+      <c r="N34" s="4">
+        <f>IF(OR(G34="",G33=""),"",G34/G33-1)</f>
+        <v/>
+      </c>
+      <c r="O34" s="4">
+        <f>IF(OR(H34="",H33=""),"",H34/H33-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O33"/>
+  <autoFilter ref="A1:O34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47858,7 +48244,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>2026-08-23 to 2026-09-24  (33 rows)</t>
         </is>
       </c>
     </row>
@@ -47870,7 +48256,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-24 20:01 local</t>
+          <t>2026-09-25 05:08 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$34</f>
+              <f>'GPU Rental'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$34</f>
+              <f>'GPU Rental'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$34</f>
+              <f>'GPU Rental'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$34</f>
+              <f>'GPU Rental'!$E$2:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$34</f>
+              <f>'GPU Rental'!$F$2:$F$35</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$34</f>
+              <f>'GPU Rental'!$G$2:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$34</f>
+              <f>'GPU Rental'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$34</f>
+              <f>'GPU Rental'!$H$2:$H$35</f>
             </numRef>
           </val>
         </ser>
@@ -1912,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3763,8 +3763,50 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="4">
+        <f>IF(OR(B35="",B34=""),"",B35/B34-1)</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>IF(OR(C35="",C34=""),"",C35/C34-1)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>IF(OR(D35="",D34=""),"",D35/D34-1)</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>IF(OR(E35="",E34=""),"",E35/E34-1)</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>IF(OR(F35="",F34=""),"",F35/F34-1)</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>IF(OR(G35="",G34=""),"",G35/G34-1)</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>IF(OR(H35="",H34=""),"",H35/H34-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O34"/>
+  <autoFilter ref="A1:O35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48244,7 +48286,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-24  (33 rows)</t>
+          <t>2026-08-23 to 2026-09-25  (34 rows)</t>
         </is>
       </c>
     </row>
@@ -48256,7 +48298,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-25 05:08 local</t>
+          <t>2026-09-25 14:37 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$34</f>
+              <f>'Daily Index'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$34</f>
+              <f>'Daily Index'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$34</f>
+              <f>'Daily Index'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$34</f>
+              <f>'Daily Index'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$34</f>
+              <f>'Daily Index'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$34</f>
+              <f>'Daily Index'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1900,8 +1900,34 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>2.0024</v>
+      </c>
+      <c r="E35" s="4">
+        <f>IF(OR(B35="",B34=""),"",B35/B34-1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>IF(OR(C35="",C34=""),"",C35/C34-1)</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>IF(OR(D35="",D34=""),"",D35/D34-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G34"/>
+  <autoFilter ref="A1:G35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3767,7 +3793,9 @@
       <c r="A35" s="10" t="n">
         <v>46290</v>
       </c>
-      <c r="B35" s="5" t="n"/>
+      <c r="B35" s="5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
@@ -48262,7 +48290,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-23  (33 rows)</t>
+          <t>2026-08-22 to 2026-09-24  (34 rows)</t>
         </is>
       </c>
     </row>
@@ -48298,7 +48326,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-25 14:37 local</t>
+          <t>2026-09-25 20:03 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$35</f>
+              <f>'Daily Index'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$35</f>
+              <f>'Daily Index'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$35</f>
+              <f>'Daily Index'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$35</f>
+              <f>'Daily Index'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$35</f>
+              <f>'Daily Index'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$35</f>
+              <f>'Daily Index'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$35</f>
+              <f>'GPU Rental'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$35</f>
+              <f>'GPU Rental'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$35</f>
+              <f>'GPU Rental'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$35</f>
+              <f>'GPU Rental'!$E$2:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$35</f>
+              <f>'GPU Rental'!$F$2:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$35</f>
+              <f>'GPU Rental'!$G$2:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$35</f>
+              <f>'GPU Rental'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$35</f>
+              <f>'GPU Rental'!$H$2:$H$36</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1926,8 +1926,34 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>0.9732</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>2.0766</v>
+      </c>
+      <c r="E36" s="4">
+        <f>IF(OR(B36="",B35=""),"",B36/B35-1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>IF(OR(C36="",C35=""),"",C36/C35-1)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>IF(OR(D36="",D35=""),"",D36/D35-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1938,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3833,8 +3859,52 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="4">
+        <f>IF(OR(B36="",B35=""),"",B36/B35-1)</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>IF(OR(C36="",C35=""),"",C36/C35-1)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>IF(OR(D36="",D35=""),"",D36/D35-1)</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>IF(OR(E36="",E35=""),"",E36/E35-1)</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>IF(OR(F36="",F35=""),"",F36/F35-1)</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>IF(OR(G36="",G35=""),"",G36/G35-1)</f>
+        <v/>
+      </c>
+      <c r="O36" s="4">
+        <f>IF(OR(H36="",H35=""),"",H36/H35-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48290,7 +48360,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-24  (34 rows)</t>
+          <t>2026-08-22 to 2026-09-25  (35 rows)</t>
         </is>
       </c>
     </row>
@@ -48314,7 +48384,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-25  (34 rows)</t>
+          <t>2026-08-23 to 2026-09-26  (35 rows)</t>
         </is>
       </c>
     </row>
@@ -48326,7 +48396,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-25 20:03 local</t>
+          <t>2026-09-26 19:15 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$36</f>
+              <f>'GPU Rental'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$36</f>
+              <f>'GPU Rental'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$36</f>
+              <f>'GPU Rental'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$36</f>
+              <f>'GPU Rental'!$E$2:$E$37</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$36</f>
+              <f>'GPU Rental'!$F$2:$F$37</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$36</f>
+              <f>'GPU Rental'!$G$2:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$36</f>
+              <f>'GPU Rental'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$36</f>
+              <f>'GPU Rental'!$H$2:$H$37</f>
             </numRef>
           </val>
         </ser>
@@ -1964,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3822,14 +3822,24 @@
       <c r="B35" s="5" t="n">
         <v>2.64</v>
       </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
+      <c r="C35" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="F35" s="5" t="n">
         <v>5.87</v>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
+      <c r="G35" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>3.75</v>
+      </c>
       <c r="I35" s="4">
         <f>IF(OR(B35="",B34=""),"",B35/B34-1)</f>
         <v/>
@@ -3866,14 +3876,24 @@
       <c r="B36" s="5" t="n">
         <v>2.72</v>
       </c>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
+      <c r="C36" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="F36" s="5" t="n">
         <v>5.87</v>
       </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
+      <c r="G36" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>3.75</v>
+      </c>
       <c r="I36" s="4">
         <f>IF(OR(B36="",B35=""),"",B36/B35-1)</f>
         <v/>
@@ -3903,8 +3923,52 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="4">
+        <f>IF(OR(B37="",B36=""),"",B37/B36-1)</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>IF(OR(C37="",C36=""),"",C37/C36-1)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>IF(OR(D37="",D36=""),"",D37/D36-1)</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>IF(OR(E37="",E36=""),"",E37/E36-1)</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>IF(OR(F37="",F36=""),"",F37/F36-1)</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>IF(OR(G37="",G36=""),"",G37/G36-1)</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>IF(OR(H37="",H36=""),"",H37/H36-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48384,7 +48448,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-26  (35 rows)</t>
+          <t>2026-08-23 to 2026-09-27  (36 rows)</t>
         </is>
       </c>
     </row>
@@ -48396,7 +48460,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-26 19:15 local</t>
+          <t>2026-09-27 14:43 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$36</f>
+              <f>'Daily Index'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$36</f>
+              <f>'Daily Index'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$36</f>
+              <f>'Daily Index'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$36</f>
+              <f>'Daily Index'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$36</f>
+              <f>'Daily Index'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$36</f>
+              <f>'Daily Index'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1952,8 +1952,34 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>2.1179</v>
+      </c>
+      <c r="E37" s="4">
+        <f>IF(OR(B37="",B36=""),"",B37/B36-1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>IF(OR(C37="",C36=""),"",C37/C36-1)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>IF(OR(D37="",D36=""),"",D37/D36-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G36"/>
+  <autoFilter ref="A1:G37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3930,14 +3956,24 @@
       <c r="B37" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="C37" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="F37" s="5" t="n">
         <v>5.87</v>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
+      <c r="G37" s="5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>3.75</v>
+      </c>
       <c r="I37" s="4">
         <f>IF(OR(B37="",B36=""),"",B37/B36-1)</f>
         <v/>
@@ -48424,7 +48460,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-25  (35 rows)</t>
+          <t>2026-08-22 to 2026-09-26  (36 rows)</t>
         </is>
       </c>
     </row>
@@ -48460,7 +48496,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-27 14:43 local</t>
+          <t>2026-09-27 19:47 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$37</f>
+              <f>'Daily Index'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$37</f>
+              <f>'Daily Index'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$37</f>
+              <f>'Daily Index'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$37</f>
+              <f>'Daily Index'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$37</f>
+              <f>'Daily Index'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$37</f>
+              <f>'Daily Index'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$37</f>
+              <f>'GPU Rental'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$37</f>
+              <f>'GPU Rental'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$37</f>
+              <f>'GPU Rental'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$37</f>
+              <f>'GPU Rental'!$E$2:$E$38</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$37</f>
+              <f>'GPU Rental'!$F$2:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$37</f>
+              <f>'GPU Rental'!$G$2:$G$38</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$37</f>
+              <f>'GPU Rental'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$37</f>
+              <f>'GPU Rental'!$H$2:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1978,8 +1978,32 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="4">
+        <f>IF(OR(B38="",B37=""),"",B38/B37-1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>IF(OR(C38="",C37=""),"",C38/C37-1)</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>IF(OR(D38="",D37=""),"",D38/D37-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1990,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4003,8 +4027,62 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I38" s="4">
+        <f>IF(OR(B38="",B37=""),"",B38/B37-1)</f>
+        <v/>
+      </c>
+      <c r="J38" s="4">
+        <f>IF(OR(C38="",C37=""),"",C38/C37-1)</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>IF(OR(D38="",D37=""),"",D38/D37-1)</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>IF(OR(E38="",E37=""),"",E38/E37-1)</f>
+        <v/>
+      </c>
+      <c r="M38" s="4">
+        <f>IF(OR(F38="",F37=""),"",F38/F37-1)</f>
+        <v/>
+      </c>
+      <c r="N38" s="4">
+        <f>IF(OR(G38="",G37=""),"",G38/G37-1)</f>
+        <v/>
+      </c>
+      <c r="O38" s="4">
+        <f>IF(OR(H38="",H37=""),"",H38/H37-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O37"/>
+  <autoFilter ref="A1:O38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48460,7 +48538,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-26  (36 rows)</t>
+          <t>2026-08-22 to 2026-09-27  (37 rows)</t>
         </is>
       </c>
     </row>
@@ -48484,7 +48562,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-27  (36 rows)</t>
+          <t>2026-08-23 to 2026-09-28  (37 rows)</t>
         </is>
       </c>
     </row>
@@ -48496,7 +48574,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-27 19:47 local</t>
+          <t>2026-09-28 17:41 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1988,7 +1987,9 @@
       <c r="C38" s="11" t="n">
         <v>0.4721</v>
       </c>
-      <c r="D38" s="11" t="n"/>
+      <c r="D38" s="11" t="n">
+        <v>2.2669</v>
+      </c>
       <c r="E38" s="4">
         <f>IF(OR(B38="",B37=""),"",B38/B37-1)</f>
         <v/>
@@ -48574,7 +48575,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-28 17:41 local</t>
+          <t>2026-09-28 22:08 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$38</f>
+              <f>'GPU Rental'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$38</f>
+              <f>'GPU Rental'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$38</f>
+              <f>'GPU Rental'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$38</f>
+              <f>'GPU Rental'!$E$2:$E$39</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$38</f>
+              <f>'GPU Rental'!$F$2:$F$39</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$38</f>
+              <f>'GPU Rental'!$G$2:$G$39</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$38</f>
+              <f>'GPU Rental'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$38</f>
+              <f>'GPU Rental'!$H$2:$H$39</f>
             </numRef>
           </val>
         </ser>
@@ -2015,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4082,8 +4083,62 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I39" s="4">
+        <f>IF(OR(B39="",B38=""),"",B39/B38-1)</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>IF(OR(C39="",C38=""),"",C39/C38-1)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>IF(OR(D39="",D38=""),"",D39/D38-1)</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>IF(OR(E39="",E38=""),"",E39/E38-1)</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>IF(OR(F39="",F38=""),"",F39/F38-1)</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>IF(OR(G39="",G38=""),"",G39/G38-1)</f>
+        <v/>
+      </c>
+      <c r="O39" s="4">
+        <f>IF(OR(H39="",H38=""),"",H39/H38-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48563,7 +48618,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-28  (37 rows)</t>
+          <t>2026-08-23 to 2026-09-29  (38 rows)</t>
         </is>
       </c>
     </row>
@@ -48575,7 +48630,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-28 22:08 local</t>
+          <t>2026-09-29 15:55 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$38</f>
+              <f>'Daily Index'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$38</f>
+              <f>'Daily Index'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$38</f>
+              <f>'Daily Index'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$38</f>
+              <f>'Daily Index'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$38</f>
+              <f>'Daily Index'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$38</f>
+              <f>'Daily Index'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2004,8 +2004,34 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>2.4178</v>
+      </c>
+      <c r="E39" s="4">
+        <f>IF(OR(B39="",B38=""),"",B39/B38-1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>IF(OR(C39="",C38=""),"",C39/C38-1)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>IF(OR(D39="",D38=""),"",D39/D38-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:G39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48594,7 +48620,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-27  (37 rows)</t>
+          <t>2026-08-22 to 2026-09-28  (38 rows)</t>
         </is>
       </c>
     </row>
@@ -48630,7 +48656,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 15:55 local</t>
+          <t>2026-09-29 20:53 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$39</f>
+              <f>'GPU Rental'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$39</f>
+              <f>'GPU Rental'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$39</f>
+              <f>'GPU Rental'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$39</f>
+              <f>'GPU Rental'!$E$2:$E$40</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$39</f>
+              <f>'GPU Rental'!$F$2:$F$40</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$39</f>
+              <f>'GPU Rental'!$G$2:$G$40</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$39</f>
+              <f>'GPU Rental'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$39</f>
+              <f>'GPU Rental'!$H$2:$H$40</f>
             </numRef>
           </val>
         </ser>
@@ -2042,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4163,8 +4163,62 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I40" s="4">
+        <f>IF(OR(B40="",B39=""),"",B40/B39-1)</f>
+        <v/>
+      </c>
+      <c r="J40" s="4">
+        <f>IF(OR(C40="",C39=""),"",C40/C39-1)</f>
+        <v/>
+      </c>
+      <c r="K40" s="4">
+        <f>IF(OR(D40="",D39=""),"",D40/D39-1)</f>
+        <v/>
+      </c>
+      <c r="L40" s="4">
+        <f>IF(OR(E40="",E39=""),"",E40/E39-1)</f>
+        <v/>
+      </c>
+      <c r="M40" s="4">
+        <f>IF(OR(F40="",F39=""),"",F40/F39-1)</f>
+        <v/>
+      </c>
+      <c r="N40" s="4">
+        <f>IF(OR(G40="",G39=""),"",G40/G39-1)</f>
+        <v/>
+      </c>
+      <c r="O40" s="4">
+        <f>IF(OR(H40="",H39=""),"",H40/H39-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48644,7 +48698,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-29  (38 rows)</t>
+          <t>2026-08-23 to 2026-09-30  (39 rows)</t>
         </is>
       </c>
     </row>
@@ -48656,7 +48710,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 20:53 local</t>
+          <t>2026-09-30 15:56 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$39</f>
+              <f>'Daily Index'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$39</f>
+              <f>'Daily Index'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$39</f>
+              <f>'Daily Index'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$39</f>
+              <f>'Daily Index'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$39</f>
+              <f>'Daily Index'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$39</f>
+              <f>'Daily Index'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2030,8 +2030,34 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>2.4904</v>
+      </c>
+      <c r="E40" s="4">
+        <f>IF(OR(B40="",B39=""),"",B40/B39-1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="4">
+        <f>IF(OR(C40="",C39=""),"",C40/C39-1)</f>
+        <v/>
+      </c>
+      <c r="G40" s="4">
+        <f>IF(OR(D40="",D39=""),"",D40/D39-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G39"/>
+  <autoFilter ref="A1:G40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48674,7 +48700,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-28  (38 rows)</t>
+          <t>2026-08-22 to 2026-09-29  (39 rows)</t>
         </is>
       </c>
     </row>
@@ -48710,7 +48736,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-30 15:56 local</t>
+          <t>2026-09-30 20:52 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$40</f>
+              <f>'Daily Index'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$40</f>
+              <f>'Daily Index'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$40</f>
+              <f>'Daily Index'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$40</f>
+              <f>'Daily Index'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$40</f>
+              <f>'Daily Index'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$40</f>
+              <f>'Daily Index'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$40</f>
+              <f>'GPU Rental'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$40</f>
+              <f>'GPU Rental'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$40</f>
+              <f>'GPU Rental'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$40</f>
+              <f>'GPU Rental'!$E$2:$E$41</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$40</f>
+              <f>'GPU Rental'!$F$2:$F$41</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$40</f>
+              <f>'GPU Rental'!$G$2:$G$41</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$40</f>
+              <f>'GPU Rental'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$40</f>
+              <f>'GPU Rental'!$H$2:$H$41</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2056,8 +2056,34 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>2.4938</v>
+      </c>
+      <c r="E41" s="4">
+        <f>IF(OR(B41="",B40=""),"",B41/B40-1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="4">
+        <f>IF(OR(C41="",C40=""),"",C41/C40-1)</f>
+        <v/>
+      </c>
+      <c r="G41" s="4">
+        <f>IF(OR(D41="",D40=""),"",D41/D40-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G40"/>
+  <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2068,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4243,8 +4269,52 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="4">
+        <f>IF(OR(B41="",B40=""),"",B41/B40-1)</f>
+        <v/>
+      </c>
+      <c r="J41" s="4">
+        <f>IF(OR(C41="",C40=""),"",C41/C40-1)</f>
+        <v/>
+      </c>
+      <c r="K41" s="4">
+        <f>IF(OR(D41="",D40=""),"",D41/D40-1)</f>
+        <v/>
+      </c>
+      <c r="L41" s="4">
+        <f>IF(OR(E41="",E40=""),"",E41/E40-1)</f>
+        <v/>
+      </c>
+      <c r="M41" s="4">
+        <f>IF(OR(F41="",F40=""),"",F41/F40-1)</f>
+        <v/>
+      </c>
+      <c r="N41" s="4">
+        <f>IF(OR(G41="",G40=""),"",G41/G40-1)</f>
+        <v/>
+      </c>
+      <c r="O41" s="4">
+        <f>IF(OR(H41="",H40=""),"",H41/H40-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48700,7 +48770,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-29  (39 rows)</t>
+          <t>2026-08-22 to 2026-09-30  (40 rows)</t>
         </is>
       </c>
     </row>
@@ -48724,7 +48794,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-09-30  (39 rows)</t>
+          <t>2026-08-23 to 2026-10-01  (40 rows)</t>
         </is>
       </c>
     </row>
@@ -48736,7 +48806,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-30 20:52 local</t>
+          <t>2026-10-01 16:28 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$41</f>
+              <f>'GPU Rental'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$41</f>
+              <f>'GPU Rental'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$41</f>
+              <f>'GPU Rental'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$41</f>
+              <f>'GPU Rental'!$E$2:$E$42</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$41</f>
+              <f>'GPU Rental'!$F$2:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$41</f>
+              <f>'GPU Rental'!$G$2:$G$42</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$41</f>
+              <f>'GPU Rental'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$41</f>
+              <f>'GPU Rental'!$H$2:$H$42</f>
             </numRef>
           </val>
         </ser>
@@ -2094,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4276,14 +4276,24 @@
       <c r="B41" s="5" t="n">
         <v>2.77</v>
       </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
+      <c r="C41" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>2.63</v>
+      </c>
       <c r="F41" s="5" t="n">
         <v>5.86</v>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
+      <c r="G41" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I41" s="4">
         <f>IF(OR(B41="",B40=""),"",B41/B40-1)</f>
         <v/>
@@ -4313,8 +4323,62 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I42" s="4">
+        <f>IF(OR(B42="",B41=""),"",B42/B41-1)</f>
+        <v/>
+      </c>
+      <c r="J42" s="4">
+        <f>IF(OR(C42="",C41=""),"",C42/C41-1)</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>IF(OR(D42="",D41=""),"",D42/D41-1)</f>
+        <v/>
+      </c>
+      <c r="L42" s="4">
+        <f>IF(OR(E42="",E41=""),"",E42/E41-1)</f>
+        <v/>
+      </c>
+      <c r="M42" s="4">
+        <f>IF(OR(F42="",F41=""),"",F42/F41-1)</f>
+        <v/>
+      </c>
+      <c r="N42" s="4">
+        <f>IF(OR(G42="",G41=""),"",G42/G41-1)</f>
+        <v/>
+      </c>
+      <c r="O42" s="4">
+        <f>IF(OR(H42="",H41=""),"",H42/H41-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48794,7 +48858,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-01  (40 rows)</t>
+          <t>2026-08-23 to 2026-10-02  (41 rows)</t>
         </is>
       </c>
     </row>
@@ -48806,7 +48870,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-01 16:28 local</t>
+          <t>2026-10-02 15:51 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$41</f>
+              <f>'Daily Index'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$41</f>
+              <f>'Daily Index'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$41</f>
+              <f>'Daily Index'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$41</f>
+              <f>'Daily Index'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$41</f>
+              <f>'Daily Index'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$41</f>
+              <f>'Daily Index'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2082,8 +2082,34 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>0.4751</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>2.2394</v>
+      </c>
+      <c r="E42" s="4">
+        <f>IF(OR(B42="",B41=""),"",B42/B41-1)</f>
+        <v/>
+      </c>
+      <c r="F42" s="4">
+        <f>IF(OR(C42="",C41=""),"",C42/C41-1)</f>
+        <v/>
+      </c>
+      <c r="G42" s="4">
+        <f>IF(OR(D42="",D41=""),"",D42/D41-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G41"/>
+  <autoFilter ref="A1:G42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48834,7 +48860,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-09-30  (40 rows)</t>
+          <t>2026-08-22 to 2026-10-01  (41 rows)</t>
         </is>
       </c>
     </row>
@@ -48870,7 +48896,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 15:51 local</t>
+          <t>2026-10-02 20:48 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$42</f>
+              <f>'GPU Rental'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$42</f>
+              <f>'GPU Rental'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$42</f>
+              <f>'GPU Rental'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$42</f>
+              <f>'GPU Rental'!$E$2:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$42</f>
+              <f>'GPU Rental'!$F$2:$F$43</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$42</f>
+              <f>'GPU Rental'!$G$2:$G$43</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$42</f>
+              <f>'GPU Rental'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$42</f>
+              <f>'GPU Rental'!$H$2:$H$43</f>
             </numRef>
           </val>
         </ser>
@@ -2120,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4403,8 +4403,52 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="4">
+        <f>IF(OR(B43="",B42=""),"",B43/B42-1)</f>
+        <v/>
+      </c>
+      <c r="J43" s="4">
+        <f>IF(OR(C43="",C42=""),"",C43/C42-1)</f>
+        <v/>
+      </c>
+      <c r="K43" s="4">
+        <f>IF(OR(D43="",D42=""),"",D43/D42-1)</f>
+        <v/>
+      </c>
+      <c r="L43" s="4">
+        <f>IF(OR(E43="",E42=""),"",E43/E42-1)</f>
+        <v/>
+      </c>
+      <c r="M43" s="4">
+        <f>IF(OR(F43="",F42=""),"",F43/F42-1)</f>
+        <v/>
+      </c>
+      <c r="N43" s="4">
+        <f>IF(OR(G43="",G42=""),"",G43/G42-1)</f>
+        <v/>
+      </c>
+      <c r="O43" s="4">
+        <f>IF(OR(H43="",H42=""),"",H43/H42-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48884,7 +48928,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-02  (41 rows)</t>
+          <t>2026-08-23 to 2026-10-03  (42 rows)</t>
         </is>
       </c>
     </row>
@@ -48896,7 +48940,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 20:48 local</t>
+          <t>2026-10-03 14:19 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -4410,14 +4409,24 @@
       <c r="B43" s="5" t="n">
         <v>2.78</v>
       </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
+      <c r="C43" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>2.63</v>
+      </c>
       <c r="F43" s="5" t="n">
         <v>5.86</v>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
+      <c r="G43" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I43" s="4">
         <f>IF(OR(B43="",B42=""),"",B43/B42-1)</f>
         <v/>
@@ -48940,7 +48949,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-03 14:19 local</t>
+          <t>2026-10-03 19:17 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -218,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$42</f>
+              <f>'Daily Index'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$42</f>
+              <f>'Daily Index'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -250,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$42</f>
+              <f>'Daily Index'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$42</f>
+              <f>'Daily Index'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$42</f>
+              <f>'Daily Index'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$42</f>
+              <f>'Daily Index'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -1004,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2107,8 +2108,34 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>0.9374</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>0.4739</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2.1578</v>
+      </c>
+      <c r="E43" s="4">
+        <f>IF(OR(B43="",B42=""),"",B43/B42-1)</f>
+        <v/>
+      </c>
+      <c r="F43" s="4">
+        <f>IF(OR(C43="",C42=""),"",C43/C42-1)</f>
+        <v/>
+      </c>
+      <c r="G43" s="4">
+        <f>IF(OR(D43="",D42=""),"",D43/D42-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G42"/>
+  <autoFilter ref="A1:G43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48913,7 +48940,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-01  (41 rows)</t>
+          <t>2026-08-22 to 2026-10-02  (42 rows)</t>
         </is>
       </c>
     </row>
@@ -48949,7 +48976,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-03 19:17 local</t>
+          <t>2026-10-04 06:49 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$43</f>
+              <f>'Daily Index'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$43</f>
+              <f>'Daily Index'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$43</f>
+              <f>'Daily Index'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$43</f>
+              <f>'Daily Index'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$43</f>
+              <f>'Daily Index'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$43</f>
+              <f>'Daily Index'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$43</f>
+              <f>'GPU Rental'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$43</f>
+              <f>'GPU Rental'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$43</f>
+              <f>'GPU Rental'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$43</f>
+              <f>'GPU Rental'!$E$2:$E$44</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$43</f>
+              <f>'GPU Rental'!$F$2:$F$44</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$43</f>
+              <f>'GPU Rental'!$G$2:$G$44</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$43</f>
+              <f>'GPU Rental'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$43</f>
+              <f>'GPU Rental'!$H$2:$H$44</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2134,8 +2134,30 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="4">
+        <f>IF(OR(B44="",B43=""),"",B44/B43-1)</f>
+        <v/>
+      </c>
+      <c r="F44" s="4">
+        <f>IF(OR(C44="",C43=""),"",C44/C43-1)</f>
+        <v/>
+      </c>
+      <c r="G44" s="4">
+        <f>IF(OR(D44="",D43=""),"",D44/D43-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G43"/>
+  <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2146,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4483,8 +4505,52 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="4">
+        <f>IF(OR(B44="",B43=""),"",B44/B43-1)</f>
+        <v/>
+      </c>
+      <c r="J44" s="4">
+        <f>IF(OR(C44="",C43=""),"",C44/C43-1)</f>
+        <v/>
+      </c>
+      <c r="K44" s="4">
+        <f>IF(OR(D44="",D43=""),"",D44/D43-1)</f>
+        <v/>
+      </c>
+      <c r="L44" s="4">
+        <f>IF(OR(E44="",E43=""),"",E44/E43-1)</f>
+        <v/>
+      </c>
+      <c r="M44" s="4">
+        <f>IF(OR(F44="",F43=""),"",F44/F43-1)</f>
+        <v/>
+      </c>
+      <c r="N44" s="4">
+        <f>IF(OR(G44="",G43=""),"",G44/G43-1)</f>
+        <v/>
+      </c>
+      <c r="O44" s="4">
+        <f>IF(OR(H44="",H43=""),"",H44/H43-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48940,7 +49006,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-02  (42 rows)</t>
+          <t>2026-08-22 to 2026-10-03  (43 rows)</t>
         </is>
       </c>
     </row>
@@ -48964,7 +49030,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-03  (42 rows)</t>
+          <t>2026-08-23 to 2026-10-04  (43 rows)</t>
         </is>
       </c>
     </row>
@@ -48976,7 +49042,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-04 06:49 local</t>
+          <t>2026-10-04 14:48 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -4512,14 +4511,24 @@
       <c r="B44" s="5" t="n">
         <v>2.78</v>
       </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
+      <c r="C44" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>2.63</v>
+      </c>
       <c r="F44" s="5" t="n">
         <v>5.86</v>
       </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
+      <c r="G44" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I44" s="4">
         <f>IF(OR(B44="",B43=""),"",B44/B43-1)</f>
         <v/>
@@ -49042,7 +49051,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-04 14:48 local</t>
+          <t>2026-10-04 19:42 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -2137,11 +2137,15 @@
       <c r="A44" s="10" t="n">
         <v>46298</v>
       </c>
-      <c r="B44" s="11" t="n"/>
+      <c r="B44" s="11" t="n">
+        <v>0.9536</v>
+      </c>
       <c r="C44" s="11" t="n">
         <v>0.4726</v>
       </c>
-      <c r="D44" s="11" t="n"/>
+      <c r="D44" s="11" t="n">
+        <v>2.2018</v>
+      </c>
       <c r="E44" s="4">
         <f>IF(OR(B44="",B43=""),"",B44/B43-1)</f>
         <v/>
@@ -49051,7 +49055,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-04 19:42 local</t>
+          <t>2026-10-05 07:02 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -218,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$44</f>
+              <f>'Daily Index'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$44</f>
+              <f>'Daily Index'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -250,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$44</f>
+              <f>'Daily Index'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$44</f>
+              <f>'Daily Index'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$44</f>
+              <f>'Daily Index'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$44</f>
+              <f>'Daily Index'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$44</f>
+              <f>'GPU Rental'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$44</f>
+              <f>'GPU Rental'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$44</f>
+              <f>'GPU Rental'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$44</f>
+              <f>'GPU Rental'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$44</f>
+              <f>'GPU Rental'!$F$2:$F$45</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$44</f>
+              <f>'GPU Rental'!$G$2:$G$45</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$44</f>
+              <f>'GPU Rental'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$44</f>
+              <f>'GPU Rental'!$H$2:$H$45</f>
             </numRef>
           </val>
         </ser>
@@ -1004,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2159,8 +2160,34 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>0.9554</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>2.2035</v>
+      </c>
+      <c r="E45" s="4">
+        <f>IF(OR(B45="",B44=""),"",B45/B44-1)</f>
+        <v/>
+      </c>
+      <c r="F45" s="4">
+        <f>IF(OR(C45="",C44=""),"",C45/C44-1)</f>
+        <v/>
+      </c>
+      <c r="G45" s="4">
+        <f>IF(OR(D45="",D44=""),"",D45/D44-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G44"/>
+  <autoFilter ref="A1:G45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2171,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4562,8 +4589,62 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I45" s="4">
+        <f>IF(OR(B45="",B44=""),"",B45/B44-1)</f>
+        <v/>
+      </c>
+      <c r="J45" s="4">
+        <f>IF(OR(C45="",C44=""),"",C45/C44-1)</f>
+        <v/>
+      </c>
+      <c r="K45" s="4">
+        <f>IF(OR(D45="",D44=""),"",D45/D44-1)</f>
+        <v/>
+      </c>
+      <c r="L45" s="4">
+        <f>IF(OR(E45="",E44=""),"",E45/E44-1)</f>
+        <v/>
+      </c>
+      <c r="M45" s="4">
+        <f>IF(OR(F45="",F44=""),"",F45/F44-1)</f>
+        <v/>
+      </c>
+      <c r="N45" s="4">
+        <f>IF(OR(G45="",G44=""),"",G45/G44-1)</f>
+        <v/>
+      </c>
+      <c r="O45" s="4">
+        <f>IF(OR(H45="",H44=""),"",H45/H44-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49019,7 +49100,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-03  (43 rows)</t>
+          <t>2026-08-22 to 2026-10-04  (44 rows)</t>
         </is>
       </c>
     </row>
@@ -49043,7 +49124,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-04  (43 rows)</t>
+          <t>2026-08-23 to 2026-10-05  (44 rows)</t>
         </is>
       </c>
     </row>
@@ -49055,7 +49136,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-05 07:02 local</t>
+          <t>2026-10-05 18:31 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$45</f>
+              <f>'GPU Rental'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$45</f>
+              <f>'GPU Rental'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$45</f>
+              <f>'GPU Rental'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$45</f>
+              <f>'GPU Rental'!$E$2:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$45</f>
+              <f>'GPU Rental'!$F$2:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$45</f>
+              <f>'GPU Rental'!$G$2:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$45</f>
+              <f>'GPU Rental'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$45</f>
+              <f>'GPU Rental'!$H$2:$H$46</f>
             </numRef>
           </val>
         </ser>
@@ -2198,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4643,8 +4643,62 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I46" s="4">
+        <f>IF(OR(B46="",B45=""),"",B46/B45-1)</f>
+        <v/>
+      </c>
+      <c r="J46" s="4">
+        <f>IF(OR(C46="",C45=""),"",C46/C45-1)</f>
+        <v/>
+      </c>
+      <c r="K46" s="4">
+        <f>IF(OR(D46="",D45=""),"",D46/D45-1)</f>
+        <v/>
+      </c>
+      <c r="L46" s="4">
+        <f>IF(OR(E46="",E45=""),"",E46/E45-1)</f>
+        <v/>
+      </c>
+      <c r="M46" s="4">
+        <f>IF(OR(F46="",F45=""),"",F46/F45-1)</f>
+        <v/>
+      </c>
+      <c r="N46" s="4">
+        <f>IF(OR(G46="",G45=""),"",G46/G45-1)</f>
+        <v/>
+      </c>
+      <c r="O46" s="4">
+        <f>IF(OR(H46="",H45=""),"",H46/H45-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O45"/>
+  <autoFilter ref="A1:O46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49124,7 +49178,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-05  (44 rows)</t>
+          <t>2026-08-23 to 2026-10-06  (45 rows)</t>
         </is>
       </c>
     </row>
@@ -49136,7 +49190,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-05 18:31 local</t>
+          <t>2026-10-06 15:59 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$45</f>
+              <f>'Daily Index'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$45</f>
+              <f>'Daily Index'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$45</f>
+              <f>'Daily Index'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$45</f>
+              <f>'Daily Index'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$45</f>
+              <f>'Daily Index'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$45</f>
+              <f>'Daily Index'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2186,8 +2186,34 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>2.2075</v>
+      </c>
+      <c r="E46" s="4">
+        <f>IF(OR(B46="",B45=""),"",B46/B45-1)</f>
+        <v/>
+      </c>
+      <c r="F46" s="4">
+        <f>IF(OR(C46="",C45=""),"",C46/C45-1)</f>
+        <v/>
+      </c>
+      <c r="G46" s="4">
+        <f>IF(OR(D46="",D45=""),"",D46/D45-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G45"/>
+  <autoFilter ref="A1:G46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49154,7 +49180,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-04  (44 rows)</t>
+          <t>2026-08-22 to 2026-10-05  (45 rows)</t>
         </is>
       </c>
     </row>
@@ -49190,7 +49216,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 15:59 local</t>
+          <t>2026-10-06 21:03 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$46</f>
+              <f>'Daily Index'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$46</f>
+              <f>'Daily Index'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$46</f>
+              <f>'Daily Index'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$46</f>
+              <f>'Daily Index'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$46</f>
+              <f>'Daily Index'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$46</f>
+              <f>'Daily Index'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$46</f>
+              <f>'GPU Rental'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$46</f>
+              <f>'GPU Rental'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$46</f>
+              <f>'GPU Rental'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$46</f>
+              <f>'GPU Rental'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$46</f>
+              <f>'GPU Rental'!$F$2:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$46</f>
+              <f>'GPU Rental'!$G$2:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$46</f>
+              <f>'GPU Rental'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$46</f>
+              <f>'GPU Rental'!$H$2:$H$47</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2212,8 +2212,32 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>2.2044</v>
+      </c>
+      <c r="E47" s="4">
+        <f>IF(OR(B47="",B46=""),"",B47/B46-1)</f>
+        <v/>
+      </c>
+      <c r="F47" s="4">
+        <f>IF(OR(C47="",C46=""),"",C47/C46-1)</f>
+        <v/>
+      </c>
+      <c r="G47" s="4">
+        <f>IF(OR(D47="",D46=""),"",D47/D46-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G46"/>
+  <autoFilter ref="A1:G47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2224,7 +2248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4723,8 +4747,60 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I47" s="4">
+        <f>IF(OR(B47="",B46=""),"",B47/B46-1)</f>
+        <v/>
+      </c>
+      <c r="J47" s="4">
+        <f>IF(OR(C47="",C46=""),"",C47/C46-1)</f>
+        <v/>
+      </c>
+      <c r="K47" s="4">
+        <f>IF(OR(D47="",D46=""),"",D47/D46-1)</f>
+        <v/>
+      </c>
+      <c r="L47" s="4">
+        <f>IF(OR(E47="",E46=""),"",E47/E46-1)</f>
+        <v/>
+      </c>
+      <c r="M47" s="4">
+        <f>IF(OR(F47="",F46=""),"",F47/F46-1)</f>
+        <v/>
+      </c>
+      <c r="N47" s="4">
+        <f>IF(OR(G47="",G46=""),"",G47/G46-1)</f>
+        <v/>
+      </c>
+      <c r="O47" s="4">
+        <f>IF(OR(H47="",H46=""),"",H47/H46-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49180,7 +49256,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-05  (45 rows)</t>
+          <t>2026-08-22 to 2026-10-06  (46 rows)</t>
         </is>
       </c>
     </row>
@@ -49204,7 +49280,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-06  (45 rows)</t>
+          <t>2026-08-23 to 2026-10-07  (46 rows)</t>
         </is>
       </c>
     </row>
@@ -49216,7 +49292,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 21:03 local</t>
+          <t>2026-10-07 16:34 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2216,7 +2215,9 @@
       <c r="A47" s="10" t="n">
         <v>46301</v>
       </c>
-      <c r="B47" s="11" t="n"/>
+      <c r="B47" s="11" t="n">
+        <v>0.9853</v>
+      </c>
       <c r="C47" s="11" t="n">
         <v>0.4698</v>
       </c>
@@ -4757,7 +4758,9 @@
       <c r="C47" s="5" t="n">
         <v>1.52</v>
       </c>
-      <c r="D47" s="5" t="n"/>
+      <c r="D47" s="5" t="n">
+        <v>3.32</v>
+      </c>
       <c r="E47" s="5" t="n">
         <v>2.64</v>
       </c>
@@ -49292,7 +49295,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-07 16:34 local</t>
+          <t>2026-10-07 21:22 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$47</f>
+              <f>'GPU Rental'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$47</f>
+              <f>'GPU Rental'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$47</f>
+              <f>'GPU Rental'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$47</f>
+              <f>'GPU Rental'!$E$2:$E$48</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$47</f>
+              <f>'GPU Rental'!$F$2:$F$48</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$47</f>
+              <f>'GPU Rental'!$G$2:$G$48</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$47</f>
+              <f>'GPU Rental'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$47</f>
+              <f>'GPU Rental'!$H$2:$H$48</f>
             </numRef>
           </val>
         </ser>
@@ -2249,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4802,8 +4803,62 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I48" s="4">
+        <f>IF(OR(B48="",B47=""),"",B48/B47-1)</f>
+        <v/>
+      </c>
+      <c r="J48" s="4">
+        <f>IF(OR(C48="",C47=""),"",C48/C47-1)</f>
+        <v/>
+      </c>
+      <c r="K48" s="4">
+        <f>IF(OR(D48="",D47=""),"",D48/D47-1)</f>
+        <v/>
+      </c>
+      <c r="L48" s="4">
+        <f>IF(OR(E48="",E47=""),"",E48/E47-1)</f>
+        <v/>
+      </c>
+      <c r="M48" s="4">
+        <f>IF(OR(F48="",F47=""),"",F48/F47-1)</f>
+        <v/>
+      </c>
+      <c r="N48" s="4">
+        <f>IF(OR(G48="",G47=""),"",G48/G47-1)</f>
+        <v/>
+      </c>
+      <c r="O48" s="4">
+        <f>IF(OR(H48="",H47=""),"",H48/H47-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
+  <autoFilter ref="A1:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49283,7 +49338,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-07  (46 rows)</t>
+          <t>2026-08-23 to 2026-10-08  (47 rows)</t>
         </is>
       </c>
     </row>
@@ -49295,7 +49350,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-07 21:22 local</t>
+          <t>2026-10-08 16:32 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$47</f>
+              <f>'Daily Index'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$47</f>
+              <f>'Daily Index'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$47</f>
+              <f>'Daily Index'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$47</f>
+              <f>'Daily Index'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$47</f>
+              <f>'Daily Index'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$47</f>
+              <f>'Daily Index'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2238,8 +2238,34 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>2.2315</v>
+      </c>
+      <c r="E48" s="4">
+        <f>IF(OR(B48="",B47=""),"",B48/B47-1)</f>
+        <v/>
+      </c>
+      <c r="F48" s="4">
+        <f>IF(OR(C48="",C47=""),"",C48/C47-1)</f>
+        <v/>
+      </c>
+      <c r="G48" s="4">
+        <f>IF(OR(D48="",D47=""),"",D48/D47-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G47"/>
+  <autoFilter ref="A1:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49314,7 +49340,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-06  (46 rows)</t>
+          <t>2026-08-22 to 2026-10-07  (47 rows)</t>
         </is>
       </c>
     </row>
@@ -49350,7 +49376,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 16:32 local</t>
+          <t>2026-10-08 21:23 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$48</f>
+              <f>'GPU Rental'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$48</f>
+              <f>'GPU Rental'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$48</f>
+              <f>'GPU Rental'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$48</f>
+              <f>'GPU Rental'!$E$2:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$48</f>
+              <f>'GPU Rental'!$F$2:$F$49</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$48</f>
+              <f>'GPU Rental'!$G$2:$G$49</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$48</f>
+              <f>'GPU Rental'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$48</f>
+              <f>'GPU Rental'!$H$2:$H$49</f>
             </numRef>
           </val>
         </ser>
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4678,7 +4678,7 @@
         <v>1.52</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>2.64</v>
@@ -4883,8 +4883,54 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="4">
+        <f>IF(OR(B49="",B48=""),"",B49/B48-1)</f>
+        <v/>
+      </c>
+      <c r="J49" s="4">
+        <f>IF(OR(C49="",C48=""),"",C49/C48-1)</f>
+        <v/>
+      </c>
+      <c r="K49" s="4">
+        <f>IF(OR(D49="",D48=""),"",D49/D48-1)</f>
+        <v/>
+      </c>
+      <c r="L49" s="4">
+        <f>IF(OR(E49="",E48=""),"",E49/E48-1)</f>
+        <v/>
+      </c>
+      <c r="M49" s="4">
+        <f>IF(OR(F49="",F48=""),"",F49/F48-1)</f>
+        <v/>
+      </c>
+      <c r="N49" s="4">
+        <f>IF(OR(G49="",G48=""),"",G49/G48-1)</f>
+        <v/>
+      </c>
+      <c r="O49" s="4">
+        <f>IF(OR(H49="",H48=""),"",H49/H48-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49364,7 +49410,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-08  (47 rows)</t>
+          <t>2026-08-23 to 2026-10-09  (48 rows)</t>
         </is>
       </c>
     </row>
@@ -49376,7 +49422,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 21:23 local</t>
+          <t>2026-10-09 16:16 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$48</f>
+              <f>'Daily Index'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$48</f>
+              <f>'Daily Index'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$48</f>
+              <f>'Daily Index'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$48</f>
+              <f>'Daily Index'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$48</f>
+              <f>'Daily Index'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$48</f>
+              <f>'Daily Index'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2264,8 +2264,34 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>2.2474</v>
+      </c>
+      <c r="E49" s="4">
+        <f>IF(OR(B49="",B48=""),"",B49/B48-1)</f>
+        <v/>
+      </c>
+      <c r="F49" s="4">
+        <f>IF(OR(C49="",C48=""),"",C49/C48-1)</f>
+        <v/>
+      </c>
+      <c r="G49" s="4">
+        <f>IF(OR(D49="",D48=""),"",D49/D48-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4890,16 +4916,24 @@
       <c r="B49" s="5" t="n">
         <v>2.85</v>
       </c>
-      <c r="C49" s="5" t="n"/>
+      <c r="C49" s="5" t="n">
+        <v>1.53</v>
+      </c>
       <c r="D49" s="5" t="n">
         <v>3.39</v>
       </c>
-      <c r="E49" s="5" t="n"/>
+      <c r="E49" s="5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="F49" s="5" t="n">
         <v>5.93</v>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
+      <c r="G49" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I49" s="4">
         <f>IF(OR(B49="",B48=""),"",B49/B48-1)</f>
         <v/>
@@ -49386,7 +49420,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-07  (47 rows)</t>
+          <t>2026-08-22 to 2026-10-08  (48 rows)</t>
         </is>
       </c>
     </row>
@@ -49422,7 +49456,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-09 16:16 local</t>
+          <t>2026-10-09 21:00 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$49</f>
+              <f>'Daily Index'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$49</f>
+              <f>'Daily Index'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$49</f>
+              <f>'Daily Index'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$49</f>
+              <f>'Daily Index'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$49</f>
+              <f>'Daily Index'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$49</f>
+              <f>'Daily Index'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$49</f>
+              <f>'GPU Rental'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$49</f>
+              <f>'GPU Rental'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$49</f>
+              <f>'GPU Rental'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$49</f>
+              <f>'GPU Rental'!$E$2:$E$50</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$49</f>
+              <f>'GPU Rental'!$F$2:$F$50</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$49</f>
+              <f>'GPU Rental'!$G$2:$G$50</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$49</f>
+              <f>'GPU Rental'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$49</f>
+              <f>'GPU Rental'!$H$2:$H$50</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2290,8 +2290,34 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>2.2486</v>
+      </c>
+      <c r="E50" s="4">
+        <f>IF(OR(B50="",B49=""),"",B50/B49-1)</f>
+        <v/>
+      </c>
+      <c r="F50" s="4">
+        <f>IF(OR(C50="",C49=""),"",C50/C49-1)</f>
+        <v/>
+      </c>
+      <c r="G50" s="4">
+        <f>IF(OR(D50="",D49=""),"",D50/D49-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:G50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2302,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4963,8 +4989,52 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="4">
+        <f>IF(OR(B50="",B49=""),"",B50/B49-1)</f>
+        <v/>
+      </c>
+      <c r="J50" s="4">
+        <f>IF(OR(C50="",C49=""),"",C50/C49-1)</f>
+        <v/>
+      </c>
+      <c r="K50" s="4">
+        <f>IF(OR(D50="",D49=""),"",D50/D49-1)</f>
+        <v/>
+      </c>
+      <c r="L50" s="4">
+        <f>IF(OR(E50="",E49=""),"",E50/E49-1)</f>
+        <v/>
+      </c>
+      <c r="M50" s="4">
+        <f>IF(OR(F50="",F49=""),"",F50/F49-1)</f>
+        <v/>
+      </c>
+      <c r="N50" s="4">
+        <f>IF(OR(G50="",G49=""),"",G50/G49-1)</f>
+        <v/>
+      </c>
+      <c r="O50" s="4">
+        <f>IF(OR(H50="",H49=""),"",H50/H49-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49420,7 +49490,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-08  (48 rows)</t>
+          <t>2026-08-22 to 2026-10-09  (49 rows)</t>
         </is>
       </c>
     </row>
@@ -49444,7 +49514,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-09  (48 rows)</t>
+          <t>2026-08-23 to 2026-10-10  (49 rows)</t>
         </is>
       </c>
     </row>
@@ -49456,7 +49526,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-09 21:00 local</t>
+          <t>2026-10-10 15:24 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -4996,14 +4995,24 @@
       <c r="B50" s="5" t="n">
         <v>2.82</v>
       </c>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
+      <c r="C50" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="F50" s="5" t="n">
         <v>5.93</v>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
+      <c r="G50" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I50" s="4">
         <f>IF(OR(B50="",B49=""),"",B50/B49-1)</f>
         <v/>
@@ -49526,7 +49535,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-10 15:24 local</t>
+          <t>2026-10-10 20:09 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$50</f>
+              <f>'GPU Rental'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -432,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$50</f>
+              <f>'GPU Rental'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -464,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$50</f>
+              <f>'GPU Rental'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -496,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$50</f>
+              <f>'GPU Rental'!$E$2:$E$51</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$50</f>
+              <f>'GPU Rental'!$F$2:$F$51</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$50</f>
+              <f>'GPU Rental'!$G$2:$G$51</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$50</f>
+              <f>'GPU Rental'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$50</f>
+              <f>'GPU Rental'!$H$2:$H$51</f>
             </numRef>
           </val>
         </ser>
@@ -2327,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5042,8 +5043,60 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I51" s="4">
+        <f>IF(OR(B51="",B50=""),"",B51/B50-1)</f>
+        <v/>
+      </c>
+      <c r="J51" s="4">
+        <f>IF(OR(C51="",C50=""),"",C51/C50-1)</f>
+        <v/>
+      </c>
+      <c r="K51" s="4">
+        <f>IF(OR(D51="",D50=""),"",D51/D50-1)</f>
+        <v/>
+      </c>
+      <c r="L51" s="4">
+        <f>IF(OR(E51="",E50=""),"",E51/E50-1)</f>
+        <v/>
+      </c>
+      <c r="M51" s="4">
+        <f>IF(OR(F51="",F50=""),"",F51/F50-1)</f>
+        <v/>
+      </c>
+      <c r="N51" s="4">
+        <f>IF(OR(G51="",G50=""),"",G51/G50-1)</f>
+        <v/>
+      </c>
+      <c r="O51" s="4">
+        <f>IF(OR(H51="",H50=""),"",H51/H50-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O50"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49523,7 +49576,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-10  (49 rows)</t>
+          <t>2026-08-23 to 2026-10-11  (50 rows)</t>
         </is>
       </c>
     </row>
@@ -49535,7 +49588,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-10 20:09 local</t>
+          <t>2026-10-11 15:45 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -28,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -5053,7 +5052,9 @@
       <c r="C51" s="5" t="n">
         <v>1.53</v>
       </c>
-      <c r="D51" s="5" t="n"/>
+      <c r="D51" s="5" t="n">
+        <v>3.44</v>
+      </c>
       <c r="E51" s="5" t="n">
         <v>2.64</v>
       </c>
@@ -49588,7 +49589,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-11 15:45 local</t>
+          <t>2026-10-11 20:22 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -28,10 +28,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -218,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$50</f>
+              <f>'Daily Index'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$50</f>
+              <f>'Daily Index'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -250,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$50</f>
+              <f>'Daily Index'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$50</f>
+              <f>'Daily Index'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$50</f>
+              <f>'Daily Index'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$50</f>
+              <f>'Daily Index'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -1004,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2315,8 +2316,34 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>0.9721</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>2.2711</v>
+      </c>
+      <c r="E51" s="4">
+        <f>IF(OR(B51="",B50=""),"",B51/B50-1)</f>
+        <v/>
+      </c>
+      <c r="F51" s="4">
+        <f>IF(OR(C51="",C50=""),"",C51/C50-1)</f>
+        <v/>
+      </c>
+      <c r="G51" s="4">
+        <f>IF(OR(D51="",D50=""),"",D51/D50-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G50"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49553,7 +49580,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-09  (49 rows)</t>
+          <t>2026-08-22 to 2026-10-10  (50 rows)</t>
         </is>
       </c>
     </row>
@@ -49589,7 +49616,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-11 20:22 local</t>
+          <t>2026-10-12 07:21 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$51</f>
+              <f>'GPU Rental'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$51</f>
+              <f>'GPU Rental'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$51</f>
+              <f>'GPU Rental'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$51</f>
+              <f>'GPU Rental'!$E$2:$E$52</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$51</f>
+              <f>'GPU Rental'!$F$2:$F$52</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$51</f>
+              <f>'GPU Rental'!$G$2:$G$52</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$51</f>
+              <f>'GPU Rental'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$51</f>
+              <f>'GPU Rental'!$H$2:$H$52</f>
             </numRef>
           </val>
         </ser>
@@ -2354,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5123,8 +5123,62 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I52" s="4">
+        <f>IF(OR(B52="",B51=""),"",B52/B51-1)</f>
+        <v/>
+      </c>
+      <c r="J52" s="4">
+        <f>IF(OR(C52="",C51=""),"",C52/C51-1)</f>
+        <v/>
+      </c>
+      <c r="K52" s="4">
+        <f>IF(OR(D52="",D51=""),"",D52/D51-1)</f>
+        <v/>
+      </c>
+      <c r="L52" s="4">
+        <f>IF(OR(E52="",E51=""),"",E52/E51-1)</f>
+        <v/>
+      </c>
+      <c r="M52" s="4">
+        <f>IF(OR(F52="",F51=""),"",F52/F51-1)</f>
+        <v/>
+      </c>
+      <c r="N52" s="4">
+        <f>IF(OR(G52="",G51=""),"",G52/G51-1)</f>
+        <v/>
+      </c>
+      <c r="O52" s="4">
+        <f>IF(OR(H52="",H51=""),"",H52/H51-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O51"/>
+  <autoFilter ref="A1:O52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49604,7 +49658,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-11  (50 rows)</t>
+          <t>2026-08-23 to 2026-10-12  (51 rows)</t>
         </is>
       </c>
     </row>
@@ -49616,7 +49670,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-12 07:21 local</t>
+          <t>2026-10-12 19:05 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$51</f>
+              <f>'Daily Index'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$51</f>
+              <f>'Daily Index'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$51</f>
+              <f>'Daily Index'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$51</f>
+              <f>'Daily Index'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$51</f>
+              <f>'Daily Index'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$51</f>
+              <f>'Daily Index'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2342,8 +2342,34 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>2.3076</v>
+      </c>
+      <c r="E52" s="4">
+        <f>IF(OR(B52="",B51=""),"",B52/B51-1)</f>
+        <v/>
+      </c>
+      <c r="F52" s="4">
+        <f>IF(OR(C52="",C51=""),"",C52/C51-1)</f>
+        <v/>
+      </c>
+      <c r="G52" s="4">
+        <f>IF(OR(D52="",D51=""),"",D52/D51-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G51"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49634,7 +49660,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-10  (50 rows)</t>
+          <t>2026-08-22 to 2026-10-11  (51 rows)</t>
         </is>
       </c>
     </row>
@@ -49670,7 +49696,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-12 19:05 local</t>
+          <t>2026-10-12 23:04 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$487</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$52</f>
+              <f>'GPU Rental'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$52</f>
+              <f>'GPU Rental'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$52</f>
+              <f>'GPU Rental'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$52</f>
+              <f>'GPU Rental'!$E$2:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$52</f>
+              <f>'GPU Rental'!$F$2:$F$53</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$52</f>
+              <f>'GPU Rental'!$G$2:$G$53</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$52</f>
+              <f>'GPU Rental'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$52</f>
+              <f>'GPU Rental'!$H$2:$H$53</f>
             </numRef>
           </val>
         </ser>
@@ -2380,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5203,8 +5203,62 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I53" s="4">
+        <f>IF(OR(B53="",B52=""),"",B53/B52-1)</f>
+        <v/>
+      </c>
+      <c r="J53" s="4">
+        <f>IF(OR(C53="",C52=""),"",C53/C52-1)</f>
+        <v/>
+      </c>
+      <c r="K53" s="4">
+        <f>IF(OR(D53="",D52=""),"",D53/D52-1)</f>
+        <v/>
+      </c>
+      <c r="L53" s="4">
+        <f>IF(OR(E53="",E52=""),"",E53/E52-1)</f>
+        <v/>
+      </c>
+      <c r="M53" s="4">
+        <f>IF(OR(F53="",F52=""),"",F53/F52-1)</f>
+        <v/>
+      </c>
+      <c r="N53" s="4">
+        <f>IF(OR(G53="",G52=""),"",G53/G52-1)</f>
+        <v/>
+      </c>
+      <c r="O53" s="4">
+        <f>IF(OR(H53="",H52=""),"",H53/H52-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O52"/>
+  <autoFilter ref="A1:O53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49684,7 +49738,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-12  (51 rows)</t>
+          <t>2026-08-23 to 2026-10-13  (52 rows)</t>
         </is>
       </c>
     </row>
@@ -49696,7 +49750,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-12 23:04 local</t>
+          <t>2026-10-13 16:58 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$785</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$52</f>
+              <f>'Daily Index'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$52</f>
+              <f>'Daily Index'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$52</f>
+              <f>'Daily Index'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$52</f>
+              <f>'Daily Index'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$52</f>
+              <f>'Daily Index'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$52</f>
+              <f>'Daily Index'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2368,8 +2368,34 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>2.3509</v>
+      </c>
+      <c r="E53" s="4">
+        <f>IF(OR(B53="",B52=""),"",B53/B52-1)</f>
+        <v/>
+      </c>
+      <c r="F53" s="4">
+        <f>IF(OR(C53="",C52=""),"",C53/C52-1)</f>
+        <v/>
+      </c>
+      <c r="G53" s="4">
+        <f>IF(OR(D53="",D52=""),"",D53/D52-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G52"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49714,7 +49740,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-11  (51 rows)</t>
+          <t>2026-08-22 to 2026-10-12  (52 rows)</t>
         </is>
       </c>
     </row>
@@ -49750,7 +49776,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-13 16:58 local</t>
+          <t>2026-10-13 21:20 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$53</f>
+              <f>'Daily Index'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$53</f>
+              <f>'Daily Index'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$53</f>
+              <f>'Daily Index'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$53</f>
+              <f>'Daily Index'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$53</f>
+              <f>'Daily Index'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$53</f>
+              <f>'Daily Index'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2394,8 +2394,34 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E54" s="4">
+        <f>IF(OR(B54="",B53=""),"",B54/B53-1)</f>
+        <v/>
+      </c>
+      <c r="F54" s="4">
+        <f>IF(OR(C54="",C53=""),"",C54/C53-1)</f>
+        <v/>
+      </c>
+      <c r="G54" s="4">
+        <f>IF(OR(D54="",D53=""),"",D54/D53-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G53"/>
+  <autoFilter ref="A1:G54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5290,14 +5316,24 @@
       <c r="B54" s="5" t="n">
         <v>2.85</v>
       </c>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
+      <c r="C54" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>2.64</v>
+      </c>
       <c r="F54" s="5" t="n">
         <v>5.95</v>
       </c>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
+      <c r="G54" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>3.76</v>
+      </c>
       <c r="I54" s="4">
         <f>IF(OR(B54="",B53=""),"",B54/B53-1)</f>
         <v/>
@@ -36984,7 +37020,6 @@
           <t>Headline</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr"/>
       <c r="D789" s="5" t="n">
         <v>55.86</v>
       </c>
@@ -37268,7 +37303,6 @@
           <t>US estimate</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr"/>
       <c r="D802" s="5" t="n">
         <v>23.8</v>
       </c>
@@ -49770,7 +49804,6 @@
           <t>Overall</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
       <c r="D494" s="8" t="n">
         <v>15.7</v>
       </c>
@@ -50531,7 +50564,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-12  (52 rows)</t>
+          <t>2026-08-22 to 2026-10-13  (53 rows)</t>
         </is>
       </c>
     </row>
@@ -50567,7 +50600,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 14:32 local</t>
+          <t>2026-10-14 20:14 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$502</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$54</f>
+              <f>'GPU Rental'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$54</f>
+              <f>'GPU Rental'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$54</f>
+              <f>'GPU Rental'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$54</f>
+              <f>'GPU Rental'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$54</f>
+              <f>'GPU Rental'!$F$2:$F$55</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$54</f>
+              <f>'GPU Rental'!$G$2:$G$55</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$54</f>
+              <f>'GPU Rental'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$54</f>
+              <f>'GPU Rental'!$H$2:$H$55</f>
             </numRef>
           </val>
         </ser>
@@ -2432,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5363,8 +5363,62 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I55" s="4">
+        <f>IF(OR(B55="",B54=""),"",B55/B54-1)</f>
+        <v/>
+      </c>
+      <c r="J55" s="4">
+        <f>IF(OR(C55="",C54=""),"",C55/C54-1)</f>
+        <v/>
+      </c>
+      <c r="K55" s="4">
+        <f>IF(OR(D55="",D54=""),"",D55/D54-1)</f>
+        <v/>
+      </c>
+      <c r="L55" s="4">
+        <f>IF(OR(E55="",E54=""),"",E55/E54-1)</f>
+        <v/>
+      </c>
+      <c r="M55" s="4">
+        <f>IF(OR(F55="",F54=""),"",F55/F54-1)</f>
+        <v/>
+      </c>
+      <c r="N55" s="4">
+        <f>IF(OR(G55="",G54=""),"",G55/G54-1)</f>
+        <v/>
+      </c>
+      <c r="O55" s="4">
+        <f>IF(OR(H55="",H54=""),"",H55/H54-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O54"/>
+  <autoFilter ref="A1:O55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50588,7 +50642,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-14  (53 rows)</t>
+          <t>2026-08-23 to 2026-10-15  (54 rows)</t>
         </is>
       </c>
     </row>
@@ -50600,7 +50654,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 20:14 local</t>
+          <t>2026-10-15 19:55 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$54</f>
+              <f>'Daily Index'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$54</f>
+              <f>'Daily Index'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$54</f>
+              <f>'Daily Index'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$54</f>
+              <f>'Daily Index'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$54</f>
+              <f>'Daily Index'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$54</f>
+              <f>'Daily Index'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2420,8 +2420,34 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>0.4656</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>2.3718</v>
+      </c>
+      <c r="E55" s="4">
+        <f>IF(OR(B55="",B54=""),"",B55/B54-1)</f>
+        <v/>
+      </c>
+      <c r="F55" s="4">
+        <f>IF(OR(C55="",C54=""),"",C55/C54-1)</f>
+        <v/>
+      </c>
+      <c r="G55" s="4">
+        <f>IF(OR(D55="",D54=""),"",D55/D54-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50618,7 +50644,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-13  (53 rows)</t>
+          <t>2026-08-22 to 2026-10-14  (54 rows)</t>
         </is>
       </c>
     </row>
@@ -50654,7 +50680,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-15 19:55 local</t>
+          <t>2026-10-16 05:52 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$55</f>
+              <f>'Daily Index'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$55</f>
+              <f>'Daily Index'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$55</f>
+              <f>'Daily Index'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$55</f>
+              <f>'Daily Index'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$55</f>
+              <f>'Daily Index'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$55</f>
+              <f>'Daily Index'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2446,8 +2446,34 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>0.9752</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>2.3806</v>
+      </c>
+      <c r="E56" s="4">
+        <f>IF(OR(B56="",B55=""),"",B56/B55-1)</f>
+        <v/>
+      </c>
+      <c r="F56" s="4">
+        <f>IF(OR(C56="",C55=""),"",C56/C55-1)</f>
+        <v/>
+      </c>
+      <c r="G56" s="4">
+        <f>IF(OR(D56="",D55=""),"",D56/D55-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50644,7 +50670,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-14  (54 rows)</t>
+          <t>2026-08-22 to 2026-10-15  (55 rows)</t>
         </is>
       </c>
     </row>
@@ -50680,7 +50706,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-16 05:52 local</t>
+          <t>2026-10-16 13:59 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$502</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$55</f>
+              <f>'GPU Rental'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$55</f>
+              <f>'GPU Rental'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$55</f>
+              <f>'GPU Rental'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$55</f>
+              <f>'GPU Rental'!$E$2:$E$56</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$55</f>
+              <f>'GPU Rental'!$F$2:$F$56</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$55</f>
+              <f>'GPU Rental'!$G$2:$G$56</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$55</f>
+              <f>'GPU Rental'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$55</f>
+              <f>'GPU Rental'!$H$2:$H$56</f>
             </numRef>
           </val>
         </ser>
@@ -2484,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5469,8 +5469,62 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I56" s="4">
+        <f>IF(OR(B56="",B55=""),"",B56/B55-1)</f>
+        <v/>
+      </c>
+      <c r="J56" s="4">
+        <f>IF(OR(C56="",C55=""),"",C56/C55-1)</f>
+        <v/>
+      </c>
+      <c r="K56" s="4">
+        <f>IF(OR(D56="",D55=""),"",D56/D55-1)</f>
+        <v/>
+      </c>
+      <c r="L56" s="4">
+        <f>IF(OR(E56="",E55=""),"",E56/E55-1)</f>
+        <v/>
+      </c>
+      <c r="M56" s="4">
+        <f>IF(OR(F56="",F55=""),"",F56/F55-1)</f>
+        <v/>
+      </c>
+      <c r="N56" s="4">
+        <f>IF(OR(G56="",G55=""),"",G56/G55-1)</f>
+        <v/>
+      </c>
+      <c r="O56" s="4">
+        <f>IF(OR(H56="",H55=""),"",H56/H55-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O55"/>
+  <autoFilter ref="A1:O56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50694,7 +50748,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-15  (54 rows)</t>
+          <t>2026-08-23 to 2026-10-16  (55 rows)</t>
         </is>
       </c>
     </row>
@@ -50706,7 +50760,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-16 13:59 local</t>
+          <t>2026-10-16 19:35 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$502</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$56</f>
+              <f>'GPU Rental'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$56</f>
+              <f>'GPU Rental'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$56</f>
+              <f>'GPU Rental'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$56</f>
+              <f>'GPU Rental'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$56</f>
+              <f>'GPU Rental'!$F$2:$F$57</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$56</f>
+              <f>'GPU Rental'!$G$2:$G$57</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$56</f>
+              <f>'GPU Rental'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$56</f>
+              <f>'GPU Rental'!$H$2:$H$57</f>
             </numRef>
           </val>
         </ser>
@@ -2484,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5523,8 +5523,62 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I57" s="4">
+        <f>IF(OR(B57="",B56=""),"",B57/B56-1)</f>
+        <v/>
+      </c>
+      <c r="J57" s="4">
+        <f>IF(OR(C57="",C56=""),"",C57/C56-1)</f>
+        <v/>
+      </c>
+      <c r="K57" s="4">
+        <f>IF(OR(D57="",D56=""),"",D57/D56-1)</f>
+        <v/>
+      </c>
+      <c r="L57" s="4">
+        <f>IF(OR(E57="",E56=""),"",E57/E56-1)</f>
+        <v/>
+      </c>
+      <c r="M57" s="4">
+        <f>IF(OR(F57="",F56=""),"",F57/F56-1)</f>
+        <v/>
+      </c>
+      <c r="N57" s="4">
+        <f>IF(OR(G57="",G56=""),"",G57/G56-1)</f>
+        <v/>
+      </c>
+      <c r="O57" s="4">
+        <f>IF(OR(H57="",H56=""),"",H57/H56-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O56"/>
+  <autoFilter ref="A1:O57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50748,7 +50802,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-16  (55 rows)</t>
+          <t>2026-08-23 to 2026-10-17  (56 rows)</t>
         </is>
       </c>
     </row>
@@ -50760,7 +50814,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-16 19:35 local</t>
+          <t>2026-10-17 18:34 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$56</f>
+              <f>'Daily Index'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$56</f>
+              <f>'Daily Index'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$56</f>
+              <f>'Daily Index'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$56</f>
+              <f>'Daily Index'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$56</f>
+              <f>'Daily Index'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$56</f>
+              <f>'Daily Index'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2472,8 +2472,34 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>2.3539</v>
+      </c>
+      <c r="E57" s="4">
+        <f>IF(OR(B57="",B56=""),"",B57/B56-1)</f>
+        <v/>
+      </c>
+      <c r="F57" s="4">
+        <f>IF(OR(C57="",C56=""),"",C57/C56-1)</f>
+        <v/>
+      </c>
+      <c r="G57" s="4">
+        <f>IF(OR(D57="",D56=""),"",D57/D56-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G56"/>
+  <autoFilter ref="A1:G57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50778,7 +50804,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-15  (55 rows)</t>
+          <t>2026-08-22 to 2026-10-16  (56 rows)</t>
         </is>
       </c>
     </row>
@@ -50814,7 +50840,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-17 18:34 local</t>
+          <t>2026-10-18 05:54 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Source" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$57</f>
+              <f>'Daily Index'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$B$2:$B$57</f>
+              <f>'Daily Index'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$57</f>
+              <f>'Daily Index'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$C$2:$C$57</f>
+              <f>'Daily Index'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily Index'!$A$2:$A$57</f>
+              <f>'Daily Index'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily Index'!$D$2:$D$57</f>
+              <f>'Daily Index'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2498,8 +2498,34 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>0.9419</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>0.4955</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>2.2573</v>
+      </c>
+      <c r="E58" s="4">
+        <f>IF(OR(B58="",B57=""),"",B58/B57-1)</f>
+        <v/>
+      </c>
+      <c r="F58" s="4">
+        <f>IF(OR(C58="",C57=""),"",C58/C57-1)</f>
+        <v/>
+      </c>
+      <c r="G58" s="4">
+        <f>IF(OR(D58="",D57=""),"",D58/D57-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50804,7 +50830,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-22 to 2026-10-16  (56 rows)</t>
+          <t>2026-08-22 to 2026-10-17  (57 rows)</t>
         </is>
       </c>
     </row>
@@ -50840,7 +50866,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-18 05:54 local</t>
+          <t>2026-10-18 13:20 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$502</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$57</f>
+              <f>'GPU Rental'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$57</f>
+              <f>'GPU Rental'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$57</f>
+              <f>'GPU Rental'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$57</f>
+              <f>'GPU Rental'!$E$2:$E$58</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$57</f>
+              <f>'GPU Rental'!$F$2:$F$58</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$57</f>
+              <f>'GPU Rental'!$G$2:$G$58</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$57</f>
+              <f>'GPU Rental'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$57</f>
+              <f>'GPU Rental'!$H$2:$H$58</f>
             </numRef>
           </val>
         </ser>
@@ -2536,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5629,8 +5629,62 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I58" s="4">
+        <f>IF(OR(B58="",B57=""),"",B58/B57-1)</f>
+        <v/>
+      </c>
+      <c r="J58" s="4">
+        <f>IF(OR(C58="",C57=""),"",C58/C57-1)</f>
+        <v/>
+      </c>
+      <c r="K58" s="4">
+        <f>IF(OR(D58="",D57=""),"",D58/D57-1)</f>
+        <v/>
+      </c>
+      <c r="L58" s="4">
+        <f>IF(OR(E58="",E57=""),"",E58/E57-1)</f>
+        <v/>
+      </c>
+      <c r="M58" s="4">
+        <f>IF(OR(F58="",F57=""),"",F58/F57-1)</f>
+        <v/>
+      </c>
+      <c r="N58" s="4">
+        <f>IF(OR(G58="",G57=""),"",G58/G57-1)</f>
+        <v/>
+      </c>
+      <c r="O58" s="4">
+        <f>IF(OR(H58="",H57=""),"",H58/H57-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O57"/>
+  <autoFilter ref="A1:O58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50854,7 +50908,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-17  (56 rows)</t>
+          <t>2026-08-23 to 2026-10-18  (57 rows)</t>
         </is>
       </c>
     </row>
@@ -50866,7 +50920,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-18 13:20 local</t>
+          <t>2026-10-18 18:42 local</t>
         </is>
       </c>
     </row>

--- a/LLM_Token_Expenditure_Index.xlsx
+++ b/LLM_Token_Expenditure_Index.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Index'!$A$1:$G$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GPU Rental'!$A$1:$O$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Forward Curve'!$A$1:$AN$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ramp Adoption'!$A$1:$F$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ramp Spend per Employee'!$A$1:$I$502</definedName>
@@ -401,12 +401,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$B$2:$B$58</f>
+              <f>'GPU Rental'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -433,12 +433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$C$2:$C$58</f>
+              <f>'GPU Rental'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +465,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$D$2:$D$58</f>
+              <f>'GPU Rental'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$E$2:$E$58</f>
+              <f>'GPU Rental'!$E$2:$E$59</f>
             </numRef>
           </val>
         </ser>
@@ -529,12 +529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$F$2:$F$58</f>
+              <f>'GPU Rental'!$F$2:$F$59</f>
             </numRef>
           </val>
         </ser>
@@ -561,12 +561,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$G$2:$G$58</f>
+              <f>'GPU Rental'!$G$2:$G$59</f>
             </numRef>
           </val>
         </ser>
@@ -593,12 +593,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GPU Rental'!$A$2:$A$58</f>
+              <f>'GPU Rental'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GPU Rental'!$H$2:$H$58</f>
+              <f>'GPU Rental'!$H$2:$H$59</f>
             </numRef>
           </val>
         </ser>
@@ -2536,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5683,8 +5683,62 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I59" s="4">
+        <f>IF(OR(B59="",B58=""),"",B59/B58-1)</f>
+        <v/>
+      </c>
+      <c r="J59" s="4">
+        <f>IF(OR(C59="",C58=""),"",C59/C58-1)</f>
+        <v/>
+      </c>
+      <c r="K59" s="4">
+        <f>IF(OR(D59="",D58=""),"",D59/D58-1)</f>
+        <v/>
+      </c>
+      <c r="L59" s="4">
+        <f>IF(OR(E59="",E58=""),"",E59/E58-1)</f>
+        <v/>
+      </c>
+      <c r="M59" s="4">
+        <f>IF(OR(F59="",F58=""),"",F59/F58-1)</f>
+        <v/>
+      </c>
+      <c r="N59" s="4">
+        <f>IF(OR(G59="",G58=""),"",G59/G58-1)</f>
+        <v/>
+      </c>
+      <c r="O59" s="4">
+        <f>IF(OR(H59="",H58=""),"",H59/H58-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O58"/>
+  <autoFilter ref="A1:O59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50908,7 +50962,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-23 to 2026-10-18  (57 rows)</t>
+          <t>2026-08-23 to 2026-10-19  (58 rows)</t>
         </is>
       </c>
     </row>
@@ -50920,7 +50974,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-18 18:42 local</t>
+          <t>2026-10-19 16:29 local</t>
         </is>
       </c>
     </row>
